--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
@@ -11,15 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="900">
   <si>
     <t>XC001</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2885,6 +2882,53 @@
   </si>
   <si>
     <t>XC324</t>
+  </si>
+  <si>
+    <t>联系：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头1：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头2或地址：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编号：</t>
+  </si>
+  <si>
+    <t>品名：</t>
+  </si>
+  <si>
+    <t>规格：</t>
+  </si>
+  <si>
+    <t>原料：</t>
+  </si>
+  <si>
+    <t>克重：</t>
+  </si>
+  <si>
+    <t>色胚：</t>
+  </si>
+  <si>
+    <t>门幅：</t>
+  </si>
+  <si>
+    <t>价格：</t>
+  </si>
+  <si>
+    <t>备注：</t>
+  </si>
+  <si>
+    <t>嘉兴市旭辰纺织有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏嘉锦纺织科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3050,7 +3094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3132,6 +3176,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3147,59 +3203,6 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet0"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="stlx_CFE32D68377D"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="14">
-          <cell r="L14" t="str">
-            <v>编号：</v>
-          </cell>
-          <cell r="N14" t="str">
-            <v>品名：</v>
-          </cell>
-          <cell r="O14" t="str">
-            <v>规格：</v>
-          </cell>
-          <cell r="P14" t="str">
-            <v>原料：</v>
-          </cell>
-          <cell r="R14" t="str">
-            <v>克重：</v>
-          </cell>
-          <cell r="S14" t="str">
-            <v>色坯：</v>
-          </cell>
-          <cell r="T14" t="str">
-            <v>门幅：</v>
-          </cell>
-          <cell r="U14" t="str">
-            <v>价格：</v>
-          </cell>
-          <cell r="V14" t="str">
-            <v>备注:（不要超12字）</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3488,51 +3491,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I325"/>
+  <dimension ref="A1:M325"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="9" width="9" style="20"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="11" max="11" width="26.75" customWidth="1"/>
+    <col min="12" max="12" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="10" t="str">
-        <f>[1]Sheet0!$L$14</f>
-        <v>编号：</v>
-      </c>
-      <c r="B1" s="11" t="str">
-        <f>[1]Sheet0!$N$14</f>
-        <v>品名：</v>
-      </c>
-      <c r="C1" s="11" t="str">
-        <f>[1]Sheet0!$O$14</f>
-        <v>规格：</v>
-      </c>
-      <c r="D1" s="11" t="str">
-        <f>[1]Sheet0!$P$14</f>
-        <v>原料：</v>
-      </c>
-      <c r="E1" s="11" t="str">
-        <f>[1]Sheet0!$R$14</f>
-        <v>克重：</v>
-      </c>
-      <c r="F1" s="11" t="str">
-        <f>[1]Sheet0!$S$14</f>
-        <v>色坯：</v>
-      </c>
-      <c r="G1" s="11" t="str">
-        <f>[1]Sheet0!$T$14</f>
-        <v>门幅：</v>
-      </c>
-      <c r="H1" s="12" t="str">
-        <f>[1]Sheet0!$U$14</f>
-        <v>价格：</v>
-      </c>
-      <c r="I1" s="12" t="str">
-        <f>[1]Sheet0!$V$14</f>
-        <v>备注:（不要超12字）</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>891</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>887</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>888</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3556,8 +3562,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="24" t="s">
+        <v>898</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>899</v>
+      </c>
+      <c r="L2" s="22">
+        <v>18962500118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -3581,8 +3596,11 @@
         <v>2.5</v>
       </c>
       <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -3606,8 +3624,11 @@
         <v>2.7</v>
       </c>
       <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -3632,7 +3653,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3657,7 +3678,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -3682,7 +3703,7 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -3707,7 +3728,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -3732,7 +3753,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -3757,7 +3778,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -3782,7 +3803,7 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:13">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -3807,7 +3828,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -3832,7 +3853,7 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -3857,7 +3878,7 @@
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -3882,7 +3903,7 @@
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
   </bookViews>
@@ -16,23 +16,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="963">
   <si>
     <t>17.5*3*27</t>
   </si>
   <si>
+    <t>XC002</t>
+  </si>
+  <si>
+    <t>1*1消光横条</t>
+  </si>
+  <si>
+    <t>17.5*3*28</t>
+  </si>
+  <si>
     <t>75*75*150</t>
   </si>
   <si>
-    <t>XC002</t>
-  </si>
-  <si>
-    <t>1*1消光横条</t>
-  </si>
-  <si>
-    <t>17.5*3*28</t>
-  </si>
-  <si>
     <t>XC003</t>
   </si>
   <si>
@@ -1989,12 +1989,6 @@
     <t>XC301</t>
   </si>
   <si>
-    <t>39梭多乐绵</t>
-  </si>
-  <si>
-    <t>16*4*39</t>
-  </si>
-  <si>
     <t>XC302</t>
   </si>
   <si>
@@ -2040,18 +2034,18 @@
     <t>80S*75酷丝绵骑兵斜</t>
   </si>
   <si>
+    <t>80S*75T400</t>
+  </si>
+  <si>
+    <t>XC311</t>
+  </si>
+  <si>
+    <t>80S*50酷丝绵</t>
+  </si>
+  <si>
     <t>18*3*43</t>
   </si>
   <si>
-    <t>80S*75T400</t>
-  </si>
-  <si>
-    <t>XC311</t>
-  </si>
-  <si>
-    <t>80S*50酷丝绵</t>
-  </si>
-  <si>
     <t>80S酷*50DT400</t>
   </si>
   <si>
@@ -2095,12 +2089,15 @@
   </si>
   <si>
     <t>联系：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>抬头1：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>抬头2或地址：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>编号：</t>
@@ -2130,837 +2127,823 @@
     <t>备注：</t>
   </si>
   <si>
-    <t>嘉兴市旭辰纺织有限公司</t>
-  </si>
-  <si>
     <t>江苏嘉锦纺织科技有限公司</t>
-  </si>
-  <si>
-    <t>13957391917   18962500118   温州路99号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉兴市旭辰纺织股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张18962500118 盛泽温州商区13幢1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>XC001</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*225*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4+30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*42</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克375</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克350</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*23</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵细双斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75*225</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>30*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>天丝棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*26.5</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*35S 酷3/3斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯370克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>240-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯310克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*35S 酷3/3斜  加厚 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+  </si>
+  <si>
+    <t>16*4+28</t>
+  </si>
+  <si>
+    <t>238克</t>
+  </si>
+  <si>
+    <t>16*4*40</t>
+  </si>
+  <si>
+    <t>120*150T800</t>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+  </si>
+  <si>
+    <t>20*2*31</t>
+  </si>
+  <si>
+    <t>37梭多乐绵</t>
+  </si>
+  <si>
+    <t>16*4*37</t>
+  </si>
+  <si>
+    <t>白坯300克</t>
+  </si>
+  <si>
+    <t>16*4*44</t>
+  </si>
+  <si>
+    <t>白坯368克</t>
+  </si>
+  <si>
+    <t>XC325</t>
+  </si>
+  <si>
+    <t>XC326</t>
+  </si>
+  <si>
+    <t>XC327</t>
+  </si>
+  <si>
+    <t>XC328</t>
+  </si>
+  <si>
+    <t>XC329</t>
+  </si>
+  <si>
+    <t>XC330</t>
+  </si>
+  <si>
+    <t>XC331</t>
+  </si>
+  <si>
+    <t>XC332</t>
+  </si>
+  <si>
+    <t>XC333</t>
+  </si>
+  <si>
+    <t>XC334</t>
+  </si>
+  <si>
+    <t>XC335</t>
+  </si>
+  <si>
+    <t>XC336</t>
+  </si>
+  <si>
+    <t>XC337</t>
+  </si>
+  <si>
+    <t>XC338</t>
+  </si>
+  <si>
+    <t>XC339</t>
+  </si>
+  <si>
+    <t>XC340</t>
+  </si>
+  <si>
+    <t>XC341</t>
+  </si>
+  <si>
+    <t>XC342</t>
+  </si>
+  <si>
+    <t>XC343</t>
+  </si>
+  <si>
+    <t>XC344</t>
+  </si>
+  <si>
+    <t>XC345</t>
+  </si>
+  <si>
+    <t>XC346</t>
+  </si>
+  <si>
+    <t>XC347</t>
+  </si>
+  <si>
+    <t>XC348</t>
+  </si>
+  <si>
+    <t>XC349</t>
+  </si>
+  <si>
+    <t>XC350</t>
+  </si>
+  <si>
+    <t>XC351</t>
+  </si>
+  <si>
+    <t>XC352</t>
+  </si>
+  <si>
+    <t>XC353</t>
+  </si>
+  <si>
+    <t>XC354</t>
+  </si>
+  <si>
+    <t>XC355</t>
+  </si>
+  <si>
+    <t>XC356</t>
+  </si>
+  <si>
+    <t>XC357</t>
+  </si>
+  <si>
+    <t>XC358</t>
+  </si>
+  <si>
+    <t>XC359</t>
+  </si>
+  <si>
+    <t>XC360</t>
+  </si>
+  <si>
+    <t>XC361</t>
+  </si>
+  <si>
+    <t>XC362</t>
+  </si>
+  <si>
+    <t>XC363</t>
+  </si>
+  <si>
+    <t>XC364</t>
+  </si>
+  <si>
+    <t>XC365</t>
+  </si>
+  <si>
+    <t>XC366</t>
+  </si>
+  <si>
+    <t>XC367</t>
+  </si>
+  <si>
+    <t>XC368</t>
+  </si>
+  <si>
+    <t>XC369</t>
+  </si>
+  <si>
+    <t>XC370</t>
+  </si>
+  <si>
+    <t>XC371</t>
+  </si>
+  <si>
+    <t>XC372</t>
+  </si>
+  <si>
+    <t>XC373</t>
+  </si>
+  <si>
+    <t>XC374</t>
+  </si>
+  <si>
+    <t>XC375</t>
+  </si>
+  <si>
+    <t>XC376</t>
+  </si>
+  <si>
+    <t>XC377</t>
+  </si>
+  <si>
+    <t>XC378</t>
+  </si>
+  <si>
+    <t>XC379</t>
+  </si>
+  <si>
+    <t>XC380</t>
+  </si>
+  <si>
+    <t>XC381</t>
+  </si>
+  <si>
+    <t>XC382</t>
+  </si>
+  <si>
+    <t>XC383</t>
+  </si>
+  <si>
+    <t>XC384</t>
+  </si>
+  <si>
+    <t>XC385</t>
+  </si>
+  <si>
+    <t>XC386</t>
+  </si>
+  <si>
+    <t>XC387</t>
+  </si>
+  <si>
+    <t>XC388</t>
+  </si>
+  <si>
+    <t>XC389</t>
+  </si>
+  <si>
+    <t>XC390</t>
+  </si>
+  <si>
+    <t>XC391</t>
+  </si>
+  <si>
+    <t>XC392</t>
+  </si>
+  <si>
+    <t>XC393</t>
+  </si>
+  <si>
+    <t>XC394</t>
+  </si>
+  <si>
+    <t>XC395</t>
+  </si>
+  <si>
+    <t>XC396</t>
+  </si>
+  <si>
+    <t>XC397</t>
+  </si>
+  <si>
+    <t>XC398</t>
+  </si>
+  <si>
+    <t>XC399</t>
+  </si>
+  <si>
+    <t>XC400</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2968,14 +2951,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2990,32 +2965,22 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -3031,7 +2996,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3040,8 +3005,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -3065,12 +3036,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3106,18 +3071,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3134,6 +3087,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3145,61 +3104,79 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <protection locked="0"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <protection locked="0"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <protection locked="0"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <protection locked="0"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <protection locked="0"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -3207,27 +3184,22 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3235,11 +3207,11 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3247,7 +3219,58 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3255,50 +3278,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3306,27 +3286,19 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3334,129 +3306,144 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="14" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="16">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 14" xfId="2"/>
+    <cellStyle name="常规 14 2" xfId="10"/>
     <cellStyle name="常规 15" xfId="3"/>
+    <cellStyle name="常规 15 2" xfId="12"/>
     <cellStyle name="常规 17" xfId="6"/>
+    <cellStyle name="常规 17 2" xfId="11"/>
     <cellStyle name="常规 2" xfId="8"/>
+    <cellStyle name="常规 2 8" xfId="15"/>
     <cellStyle name="常规 3 2" xfId="4"/>
     <cellStyle name="常规 3 2 2" xfId="5"/>
+    <cellStyle name="常规 3 2 2 2" xfId="13"/>
     <cellStyle name="常规 4 3" xfId="1"/>
+    <cellStyle name="常规 4 3 2" xfId="9"/>
     <cellStyle name="常规 6" xfId="7"/>
+    <cellStyle name="常规 6 2" xfId="14"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3748,114 +3735,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M325"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:M401"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="9" width="9" style="1"/>
+    <col min="1" max="9" width="9" style="4"/>
     <col min="10" max="10" width="27" customWidth="1"/>
     <col min="11" max="11" width="26.75" customWidth="1"/>
     <col min="12" max="12" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>703</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>709</v>
+        <v>4</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
       </c>
       <c r="F2" s="9"/>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>165</v>
       </c>
       <c r="H2" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="6" t="s">
+      <c r="I2" s="11"/>
+      <c r="J2" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>704</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E3" s="10">
         <v>80</v>
       </c>
       <c r="F3" s="9"/>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>165</v>
       </c>
       <c r="H3" s="10">
         <v>2.5</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="I3" s="11"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
@@ -3868,22 +3856,22 @@
         <v>7</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" s="10">
         <v>85</v>
       </c>
       <c r="F4" s="9"/>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>165</v>
       </c>
       <c r="H4" s="10">
         <v>2.7</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="I4" s="11"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
@@ -3893,22 +3881,22 @@
         <v>9</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E5" s="10">
         <v>78</v>
       </c>
       <c r="F5" s="9"/>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <v>165</v>
       </c>
       <c r="H5" s="10">
         <v>2.4</v>
       </c>
-      <c r="I5" s="12"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="9" t="s">
@@ -3918,22 +3906,22 @@
         <v>11</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E6" s="10">
         <v>78</v>
       </c>
       <c r="F6" s="9"/>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <v>165</v>
       </c>
       <c r="H6" s="10">
         <v>2.4</v>
       </c>
-      <c r="I6" s="12"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
@@ -3943,22 +3931,22 @@
         <v>13</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E7" s="10">
         <v>80</v>
       </c>
       <c r="F7" s="9"/>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>165</v>
       </c>
       <c r="H7" s="10">
         <v>2.4</v>
       </c>
-      <c r="I7" s="12"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
@@ -3977,13 +3965,13 @@
         <v>105</v>
       </c>
       <c r="F8" s="9"/>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <v>165</v>
       </c>
       <c r="H8" s="10">
         <v>2.6</v>
       </c>
-      <c r="I8" s="12"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="9" t="s">
@@ -4002,13 +3990,13 @@
         <v>103</v>
       </c>
       <c r="F9" s="9"/>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <v>165</v>
       </c>
       <c r="H9" s="10">
         <v>2.8</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
@@ -4018,22 +4006,22 @@
         <v>21</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E10" s="10">
         <v>73</v>
       </c>
       <c r="F10" s="9"/>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>165</v>
       </c>
       <c r="H10" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
@@ -4043,22 +4031,22 @@
         <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E11" s="10">
         <v>70</v>
       </c>
       <c r="F11" s="9"/>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>165</v>
       </c>
       <c r="H11" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I11" s="12"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
@@ -4071,19 +4059,19 @@
         <v>0</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="10">
         <v>70</v>
       </c>
       <c r="F12" s="9"/>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>165</v>
       </c>
       <c r="H12" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I12" s="12"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
@@ -4096,19 +4084,19 @@
         <v>0</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="10">
         <v>70</v>
       </c>
       <c r="F13" s="9"/>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <v>165</v>
       </c>
       <c r="H13" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I13" s="12"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="9" t="s">
@@ -4118,22 +4106,22 @@
         <v>29</v>
       </c>
       <c r="C14" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E14" s="10">
         <v>70</v>
       </c>
       <c r="F14" s="9"/>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <v>165</v>
       </c>
       <c r="H14" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I14" s="12"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
@@ -4146,19 +4134,19 @@
         <v>32</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="10">
         <v>71</v>
       </c>
       <c r="F15" s="9"/>
-      <c r="G15" s="12">
+      <c r="G15" s="11">
         <v>165</v>
       </c>
       <c r="H15" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I15" s="12"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="9" t="s">
@@ -4168,22 +4156,22 @@
         <v>34</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E16" s="10">
         <v>79</v>
       </c>
       <c r="F16" s="9"/>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>165</v>
       </c>
       <c r="H16" s="10">
         <v>2.4</v>
       </c>
-      <c r="I16" s="12"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="9" t="s">
@@ -4193,22 +4181,22 @@
         <v>36</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E17" s="10">
         <v>73</v>
       </c>
       <c r="F17" s="9"/>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <v>165</v>
       </c>
       <c r="H17" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I17" s="12"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="9" t="s">
@@ -4218,7 +4206,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>39</v>
@@ -4227,13 +4215,13 @@
         <v>67</v>
       </c>
       <c r="F18" s="9"/>
-      <c r="G18" s="12">
+      <c r="G18" s="11">
         <v>165</v>
       </c>
       <c r="H18" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I18" s="12"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="9" t="s">
@@ -4252,13 +4240,13 @@
         <v>82</v>
       </c>
       <c r="F19" s="9"/>
-      <c r="G19" s="12">
+      <c r="G19" s="11">
         <v>165</v>
       </c>
       <c r="H19" s="10">
         <v>2.7</v>
       </c>
-      <c r="I19" s="12"/>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="9" t="s">
@@ -4277,13 +4265,13 @@
         <v>68</v>
       </c>
       <c r="F20" s="9"/>
-      <c r="G20" s="12">
+      <c r="G20" s="11">
         <v>165</v>
       </c>
       <c r="H20" s="10">
         <v>2.5</v>
       </c>
-      <c r="I20" s="12"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="9" t="s">
@@ -4302,13 +4290,13 @@
         <v>68</v>
       </c>
       <c r="F21" s="9"/>
-      <c r="G21" s="12">
+      <c r="G21" s="11">
         <v>165</v>
       </c>
       <c r="H21" s="10">
         <v>2.5</v>
       </c>
-      <c r="I21" s="12"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="9" t="s">
@@ -4327,13 +4315,13 @@
         <v>65</v>
       </c>
       <c r="F22" s="9"/>
-      <c r="G22" s="12">
+      <c r="G22" s="11">
         <v>165</v>
       </c>
       <c r="H22" s="10">
         <v>2.7</v>
       </c>
-      <c r="I22" s="12"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="9" t="s">
@@ -4352,13 +4340,13 @@
         <v>68</v>
       </c>
       <c r="F23" s="9"/>
-      <c r="G23" s="12">
+      <c r="G23" s="11">
         <v>165</v>
       </c>
       <c r="H23" s="10">
         <v>2.6</v>
       </c>
-      <c r="I23" s="12"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="9" t="s">
@@ -4377,13 +4365,13 @@
         <v>68</v>
       </c>
       <c r="F24" s="9"/>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>165</v>
       </c>
       <c r="H24" s="10">
         <v>2.7</v>
       </c>
-      <c r="I24" s="12"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="9" t="s">
@@ -4402,13 +4390,13 @@
         <v>68</v>
       </c>
       <c r="F25" s="9"/>
-      <c r="G25" s="12">
+      <c r="G25" s="11">
         <v>165</v>
       </c>
       <c r="H25" s="10">
         <v>2.7</v>
       </c>
-      <c r="I25" s="12"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="9" t="s">
@@ -4421,19 +4409,19 @@
         <v>60</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="10">
         <v>75</v>
       </c>
       <c r="F26" s="9"/>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>165</v>
       </c>
       <c r="H26" s="10">
         <v>2.5</v>
       </c>
-      <c r="I26" s="12"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="9" t="s">
@@ -4446,19 +4434,19 @@
         <v>63</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="10">
         <v>84</v>
       </c>
       <c r="F27" s="9"/>
-      <c r="G27" s="12">
+      <c r="G27" s="11">
         <v>165</v>
       </c>
       <c r="H27" s="10">
         <v>2.8</v>
       </c>
-      <c r="I27" s="12"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="9" t="s">
@@ -4477,13 +4465,13 @@
         <v>68</v>
       </c>
       <c r="F28" s="9"/>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>165</v>
       </c>
       <c r="H28" s="10">
         <v>2.6</v>
       </c>
-      <c r="I28" s="12"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="9" t="s">
@@ -4493,7 +4481,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4501,14 +4489,14 @@
       <c r="E29" s="10">
         <v>68</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="12">
+      <c r="F29" s="12"/>
+      <c r="G29" s="11">
         <v>165</v>
       </c>
       <c r="H29" s="10">
         <v>2.5</v>
       </c>
-      <c r="I29" s="12"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="9" t="s">
@@ -4518,7 +4506,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -4527,13 +4515,13 @@
         <v>70</v>
       </c>
       <c r="F30" s="9"/>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>165</v>
       </c>
       <c r="H30" s="10">
         <v>2.7</v>
       </c>
-      <c r="I30" s="12"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="9" t="s">
@@ -4552,13 +4540,13 @@
         <v>65</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="12">
+      <c r="G31" s="11">
         <v>165</v>
       </c>
       <c r="H31" s="10">
         <v>2.7</v>
       </c>
-      <c r="I31" s="12"/>
+      <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="9" t="s">
@@ -4577,13 +4565,13 @@
         <v>65</v>
       </c>
       <c r="F32" s="9"/>
-      <c r="G32" s="12">
+      <c r="G32" s="11">
         <v>165</v>
       </c>
       <c r="H32" s="10">
         <v>2.6</v>
       </c>
-      <c r="I32" s="12"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="9" t="s">
@@ -4602,13 +4590,13 @@
         <v>65</v>
       </c>
       <c r="F33" s="9"/>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>165</v>
       </c>
       <c r="H33" s="10">
         <v>2.5</v>
       </c>
-      <c r="I33" s="12"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="9" t="s">
@@ -4627,13 +4615,13 @@
         <v>118</v>
       </c>
       <c r="F34" s="9"/>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>173</v>
       </c>
       <c r="H34" s="10">
         <v>3.1</v>
       </c>
-      <c r="I34" s="12"/>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="9" t="s">
@@ -4652,13 +4640,13 @@
         <v>95</v>
       </c>
       <c r="F35" s="9"/>
-      <c r="G35" s="12">
+      <c r="G35" s="11">
         <v>165</v>
       </c>
       <c r="H35" s="10">
         <v>2.6</v>
       </c>
-      <c r="I35" s="12"/>
+      <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="9" t="s">
@@ -4677,13 +4665,13 @@
         <v>103</v>
       </c>
       <c r="F36" s="9"/>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>165</v>
       </c>
       <c r="H36" s="10">
         <v>2.7</v>
       </c>
-      <c r="I36" s="12"/>
+      <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="9" t="s">
@@ -4702,13 +4690,13 @@
         <v>101</v>
       </c>
       <c r="F37" s="9"/>
-      <c r="G37" s="12">
+      <c r="G37" s="11">
         <v>165</v>
       </c>
       <c r="H37" s="10">
         <v>2.7</v>
       </c>
-      <c r="I37" s="12"/>
+      <c r="I37" s="11"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="9" t="s">
@@ -4727,13 +4715,13 @@
         <v>90</v>
       </c>
       <c r="F38" s="9"/>
-      <c r="G38" s="12">
+      <c r="G38" s="11">
         <v>165</v>
       </c>
       <c r="H38" s="10">
         <v>2.8</v>
       </c>
-      <c r="I38" s="12"/>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="9" t="s">
@@ -4746,44 +4734,44 @@
         <v>88</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" s="10">
         <v>71</v>
       </c>
       <c r="F39" s="9"/>
-      <c r="G39" s="12">
+      <c r="G39" s="11">
         <v>165</v>
       </c>
       <c r="H39" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I39" s="12"/>
+      <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="13">
         <v>70</v>
       </c>
       <c r="F40" s="9"/>
-      <c r="G40" s="12">
+      <c r="G40" s="11">
         <v>188</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H40" s="13">
         <v>2.4</v>
       </c>
-      <c r="I40" s="12"/>
+      <c r="I40" s="11"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="9" t="s">
@@ -4793,7 +4781,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>98</v>
@@ -4802,13 +4790,13 @@
         <v>72</v>
       </c>
       <c r="F41" s="9"/>
-      <c r="G41" s="12">
+      <c r="G41" s="11">
         <v>165</v>
       </c>
       <c r="H41" s="10">
         <v>2.4</v>
       </c>
-      <c r="I41" s="12"/>
+      <c r="I41" s="11"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="9" t="s">
@@ -4821,19 +4809,19 @@
         <v>7</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E42" s="10">
         <v>88</v>
       </c>
       <c r="F42" s="9"/>
-      <c r="G42" s="12">
+      <c r="G42" s="11">
         <v>165</v>
       </c>
       <c r="H42" s="10">
         <v>2.6</v>
       </c>
-      <c r="I42" s="12"/>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="9" t="s">
@@ -4852,13 +4840,13 @@
         <v>76</v>
       </c>
       <c r="F43" s="9"/>
-      <c r="G43" s="12">
+      <c r="G43" s="11">
         <v>165</v>
       </c>
       <c r="H43" s="10">
         <v>2.9</v>
       </c>
-      <c r="I43" s="12"/>
+      <c r="I43" s="11"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="9" t="s">
@@ -4877,367 +4865,367 @@
         <v>72</v>
       </c>
       <c r="F44" s="9"/>
-      <c r="G44" s="12">
+      <c r="G44" s="11">
         <v>165</v>
       </c>
       <c r="H44" s="10">
         <v>2.9</v>
       </c>
-      <c r="I44" s="12"/>
+      <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="15">
         <v>90</v>
       </c>
       <c r="F45" s="9"/>
-      <c r="G45" s="12">
-        <v>165</v>
-      </c>
-      <c r="H45" s="15">
+      <c r="G45" s="11">
+        <v>165</v>
+      </c>
+      <c r="H45" s="14">
         <v>4.7</v>
       </c>
-      <c r="I45" s="12"/>
+      <c r="I45" s="11"/>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="16" t="s">
+      <c r="C46" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="15">
         <v>110</v>
       </c>
       <c r="F46" s="9"/>
-      <c r="G46" s="12">
-        <v>165</v>
-      </c>
-      <c r="H46" s="16">
+      <c r="G46" s="11">
+        <v>165</v>
+      </c>
+      <c r="H46" s="15">
         <v>3.1</v>
       </c>
-      <c r="I46" s="12"/>
+      <c r="I46" s="11"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="15">
         <v>73</v>
       </c>
       <c r="F47" s="9"/>
-      <c r="G47" s="12">
-        <v>165</v>
-      </c>
-      <c r="H47" s="16">
+      <c r="G47" s="11">
+        <v>165</v>
+      </c>
+      <c r="H47" s="15">
         <v>3</v>
       </c>
-      <c r="I47" s="12"/>
+      <c r="I47" s="11"/>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="14">
         <v>77</v>
       </c>
-      <c r="F48" s="13"/>
-      <c r="G48" s="12">
-        <v>165</v>
-      </c>
-      <c r="H48" s="15">
+      <c r="F48" s="12"/>
+      <c r="G48" s="11">
+        <v>165</v>
+      </c>
+      <c r="H48" s="14">
         <v>3.1</v>
       </c>
-      <c r="I48" s="12"/>
+      <c r="I48" s="11"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D49" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="16">
+      <c r="D49" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="15">
         <v>85</v>
       </c>
       <c r="F49" s="9"/>
-      <c r="G49" s="12">
-        <v>165</v>
-      </c>
-      <c r="H49" s="16">
+      <c r="G49" s="11">
+        <v>165</v>
+      </c>
+      <c r="H49" s="15">
         <v>2.7</v>
       </c>
-      <c r="I49" s="12"/>
+      <c r="I49" s="11"/>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="15">
         <v>92</v>
       </c>
       <c r="F50" s="9"/>
-      <c r="G50" s="12">
-        <v>165</v>
-      </c>
-      <c r="H50" s="16">
+      <c r="G50" s="11">
+        <v>165</v>
+      </c>
+      <c r="H50" s="15">
         <v>2.6</v>
       </c>
-      <c r="I50" s="12"/>
+      <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="15">
         <v>92</v>
       </c>
       <c r="F51" s="9"/>
-      <c r="G51" s="12">
-        <v>165</v>
-      </c>
-      <c r="H51" s="16">
+      <c r="G51" s="11">
+        <v>165</v>
+      </c>
+      <c r="H51" s="15">
         <v>2.9</v>
       </c>
-      <c r="I51" s="12"/>
+      <c r="I51" s="11"/>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="16">
+      <c r="D52" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="15">
         <v>85</v>
       </c>
       <c r="F52" s="9"/>
-      <c r="G52" s="12">
-        <v>165</v>
-      </c>
-      <c r="H52" s="16">
+      <c r="G52" s="11">
+        <v>165</v>
+      </c>
+      <c r="H52" s="15">
         <v>2.5</v>
       </c>
-      <c r="I52" s="12"/>
+      <c r="I52" s="11"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="15">
         <v>115</v>
       </c>
       <c r="F53" s="9"/>
-      <c r="G53" s="12">
-        <v>165</v>
-      </c>
-      <c r="H53" s="16">
-        <v>3.3</v>
-      </c>
-      <c r="I53" s="12"/>
+      <c r="G53" s="11">
+        <v>165</v>
+      </c>
+      <c r="H53" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="I53" s="11"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="14">
+      <c r="D54" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="13">
         <v>110</v>
       </c>
       <c r="F54" s="9"/>
-      <c r="G54" s="12">
+      <c r="G54" s="11">
         <v>184</v>
       </c>
-      <c r="H54" s="14">
+      <c r="H54" s="13">
         <v>3.8</v>
       </c>
-      <c r="I54" s="12"/>
+      <c r="I54" s="11"/>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E55" s="14">
+      <c r="E55" s="13">
         <v>90</v>
       </c>
       <c r="F55" s="9">
         <v>113</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="11">
         <v>188</v>
       </c>
-      <c r="H55" s="14">
+      <c r="H55" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I55" s="12"/>
+      <c r="I55" s="11"/>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>712</v>
-      </c>
-      <c r="D56" s="14" t="s">
+      <c r="C56" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="D56" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E56" s="14">
+      <c r="E56" s="13">
         <v>90</v>
       </c>
       <c r="F56" s="9"/>
-      <c r="G56" s="12">
+      <c r="G56" s="11">
         <v>188</v>
       </c>
-      <c r="H56" s="14">
+      <c r="H56" s="13">
         <v>2.1</v>
       </c>
-      <c r="I56" s="12"/>
+      <c r="I56" s="11"/>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E57" s="14">
+      <c r="E57" s="13">
         <v>61</v>
       </c>
       <c r="F57" s="9">
         <v>80</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G57" s="11">
         <v>188</v>
       </c>
-      <c r="H57" s="14">
+      <c r="H57" s="13">
         <v>2</v>
       </c>
-      <c r="I57" s="12"/>
+      <c r="I57" s="11"/>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E58" s="13">
         <v>49</v>
       </c>
       <c r="F58" s="9"/>
-      <c r="G58" s="12">
+      <c r="G58" s="11">
         <v>188</v>
       </c>
-      <c r="H58" s="14">
+      <c r="H58" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I58" s="12"/>
+      <c r="I58" s="11"/>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="9" t="s">
@@ -5255,14 +5243,14 @@
       <c r="E59" s="10">
         <v>100</v>
       </c>
-      <c r="F59" s="11"/>
-      <c r="G59" s="12">
+      <c r="F59" s="17"/>
+      <c r="G59" s="11">
         <v>165</v>
       </c>
       <c r="H59" s="10">
         <v>2.6</v>
       </c>
-      <c r="I59" s="12"/>
+      <c r="I59" s="11"/>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="9" t="s">
@@ -5281,13 +5269,13 @@
         <v>100</v>
       </c>
       <c r="F60" s="9"/>
-      <c r="G60" s="12">
+      <c r="G60" s="11">
         <v>165</v>
       </c>
       <c r="H60" s="10">
         <v>3.2</v>
       </c>
-      <c r="I60" s="12"/>
+      <c r="I60" s="11"/>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="9" t="s">
@@ -5305,14 +5293,14 @@
       <c r="E61" s="18">
         <v>95</v>
       </c>
-      <c r="F61" s="11"/>
-      <c r="G61" s="12">
+      <c r="F61" s="17"/>
+      <c r="G61" s="11">
         <v>165</v>
       </c>
       <c r="H61" s="18">
         <v>2.7</v>
       </c>
-      <c r="I61" s="12"/>
+      <c r="I61" s="11"/>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="9" t="s">
@@ -5330,14 +5318,14 @@
       <c r="E62" s="18">
         <v>108</v>
       </c>
-      <c r="F62" s="11"/>
-      <c r="G62" s="12">
+      <c r="F62" s="17"/>
+      <c r="G62" s="11">
         <v>165</v>
       </c>
       <c r="H62" s="18">
         <v>2.6</v>
       </c>
-      <c r="I62" s="12"/>
+      <c r="I62" s="11"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="9" t="s">
@@ -5356,13 +5344,13 @@
         <v>91</v>
       </c>
       <c r="F63" s="9"/>
-      <c r="G63" s="12">
+      <c r="G63" s="11">
         <v>165</v>
       </c>
       <c r="H63" s="18">
         <v>2.5</v>
       </c>
-      <c r="I63" s="12"/>
+      <c r="I63" s="11"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="9" t="s">
@@ -5381,13 +5369,13 @@
         <v>98</v>
       </c>
       <c r="F64" s="9"/>
-      <c r="G64" s="12">
+      <c r="G64" s="11">
         <v>165</v>
       </c>
       <c r="H64" s="18">
         <v>2.6</v>
       </c>
-      <c r="I64" s="12"/>
+      <c r="I64" s="11"/>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="9" t="s">
@@ -5406,13 +5394,13 @@
         <v>103</v>
       </c>
       <c r="F65" s="9"/>
-      <c r="G65" s="12">
+      <c r="G65" s="11">
         <v>165</v>
       </c>
       <c r="H65" s="18">
         <v>2.7</v>
       </c>
-      <c r="I65" s="12"/>
+      <c r="I65" s="11"/>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="9" t="s">
@@ -5431,13 +5419,13 @@
         <v>108</v>
       </c>
       <c r="F66" s="9"/>
-      <c r="G66" s="12">
+      <c r="G66" s="11">
         <v>165</v>
       </c>
       <c r="H66" s="18">
         <v>2.9</v>
       </c>
-      <c r="I66" s="12"/>
+      <c r="I66" s="11"/>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="9" t="s">
@@ -5455,14 +5443,14 @@
       <c r="E67" s="19">
         <v>105</v>
       </c>
-      <c r="F67" s="11"/>
+      <c r="F67" s="17"/>
       <c r="G67" s="20">
         <v>165</v>
       </c>
       <c r="H67" s="19">
         <v>2.8</v>
       </c>
-      <c r="I67" s="12"/>
+      <c r="I67" s="11"/>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="9" t="s">
@@ -5481,13 +5469,13 @@
         <v>60</v>
       </c>
       <c r="F68" s="9"/>
-      <c r="G68" s="12">
+      <c r="G68" s="11">
         <v>165</v>
       </c>
       <c r="H68" s="10">
         <v>2</v>
       </c>
-      <c r="I68" s="12"/>
+      <c r="I68" s="11"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="9" t="s">
@@ -5506,13 +5494,13 @@
         <v>70</v>
       </c>
       <c r="F69" s="9"/>
-      <c r="G69" s="12">
+      <c r="G69" s="11">
         <v>165</v>
       </c>
       <c r="H69" s="10">
         <v>2.1</v>
       </c>
-      <c r="I69" s="12"/>
+      <c r="I69" s="11"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="9" t="s">
@@ -5531,13 +5519,13 @@
         <v>70</v>
       </c>
       <c r="F70" s="9"/>
-      <c r="G70" s="12">
+      <c r="G70" s="11">
         <v>165</v>
       </c>
       <c r="H70" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I70" s="12"/>
+      <c r="I70" s="11"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="9" t="s">
@@ -5556,13 +5544,13 @@
         <v>72</v>
       </c>
       <c r="F71" s="9"/>
-      <c r="G71" s="12">
+      <c r="G71" s="11">
         <v>165</v>
       </c>
       <c r="H71" s="10">
         <v>2.1</v>
       </c>
-      <c r="I71" s="12"/>
+      <c r="I71" s="11"/>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="9" t="s">
@@ -5577,17 +5565,17 @@
       <c r="D72" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E72" s="12">
+      <c r="E72" s="11">
         <v>77</v>
       </c>
-      <c r="F72" s="13"/>
-      <c r="G72" s="12">
-        <v>165</v>
-      </c>
-      <c r="H72" s="12">
+      <c r="F72" s="12"/>
+      <c r="G72" s="11">
+        <v>165</v>
+      </c>
+      <c r="H72" s="11">
         <v>2.1</v>
       </c>
-      <c r="I72" s="12"/>
+      <c r="I72" s="11"/>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="9" t="s">
@@ -5606,13 +5594,13 @@
         <v>72</v>
       </c>
       <c r="F73" s="9"/>
-      <c r="G73" s="12">
+      <c r="G73" s="11">
         <v>165</v>
       </c>
       <c r="H73" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I73" s="12"/>
+      <c r="I73" s="11"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="9" t="s">
@@ -5631,13 +5619,13 @@
         <v>80</v>
       </c>
       <c r="F74" s="9"/>
-      <c r="G74" s="12">
+      <c r="G74" s="11">
         <v>165</v>
       </c>
       <c r="H74" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I74" s="12"/>
+      <c r="I74" s="11"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="9" t="s">
@@ -5656,13 +5644,13 @@
         <v>80</v>
       </c>
       <c r="F75" s="9"/>
-      <c r="G75" s="12">
+      <c r="G75" s="11">
         <v>165</v>
       </c>
       <c r="H75" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I75" s="12"/>
+      <c r="I75" s="11"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="9" t="s">
@@ -5681,13 +5669,13 @@
         <v>82</v>
       </c>
       <c r="F76" s="9"/>
-      <c r="G76" s="12">
+      <c r="G76" s="11">
         <v>165</v>
       </c>
       <c r="H76" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I76" s="12"/>
+      <c r="I76" s="11"/>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="9" t="s">
@@ -5697,7 +5685,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>713</v>
+        <v>73</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>144</v>
@@ -5706,13 +5694,13 @@
         <v>60</v>
       </c>
       <c r="F77" s="9"/>
-      <c r="G77" s="12">
+      <c r="G77" s="11">
         <v>165</v>
       </c>
       <c r="H77" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I77" s="12"/>
+      <c r="I77" s="11"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="9" t="s">
@@ -5731,38 +5719,38 @@
         <v>63</v>
       </c>
       <c r="F78" s="9"/>
-      <c r="G78" s="12">
+      <c r="G78" s="11">
         <v>165</v>
       </c>
       <c r="H78" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I78" s="12"/>
+      <c r="I78" s="11"/>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="11" t="s">
         <v>144</v>
       </c>
       <c r="E79" s="10">
         <v>64</v>
       </c>
       <c r="F79" s="9"/>
-      <c r="G79" s="12">
+      <c r="G79" s="11">
         <v>174</v>
       </c>
-      <c r="H79" s="12">
+      <c r="H79" s="11">
         <v>2.4</v>
       </c>
-      <c r="I79" s="12"/>
+      <c r="I79" s="11"/>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="9" t="s">
@@ -5781,13 +5769,13 @@
         <v>65</v>
       </c>
       <c r="F80" s="9"/>
-      <c r="G80" s="12">
+      <c r="G80" s="11">
         <v>165</v>
       </c>
       <c r="H80" s="10">
         <v>2.5</v>
       </c>
-      <c r="I80" s="12"/>
+      <c r="I80" s="11"/>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="9" t="s">
@@ -5806,13 +5794,13 @@
         <v>60</v>
       </c>
       <c r="F81" s="9"/>
-      <c r="G81" s="12">
+      <c r="G81" s="11">
         <v>165</v>
       </c>
       <c r="H81" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I81" s="12"/>
+      <c r="I81" s="11"/>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="9" t="s">
@@ -5831,13 +5819,13 @@
         <v>68</v>
       </c>
       <c r="F82" s="9"/>
-      <c r="G82" s="12">
+      <c r="G82" s="11">
         <v>165</v>
       </c>
       <c r="H82" s="10">
         <v>2.7</v>
       </c>
-      <c r="I82" s="12"/>
+      <c r="I82" s="11"/>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="9" t="s">
@@ -5856,13 +5844,13 @@
         <v>98</v>
       </c>
       <c r="F83" s="9"/>
-      <c r="G83" s="12">
+      <c r="G83" s="11">
         <v>165</v>
       </c>
       <c r="H83" s="10">
         <v>3.2</v>
       </c>
-      <c r="I83" s="12"/>
+      <c r="I83" s="11"/>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="9" t="s">
@@ -5881,13 +5869,13 @@
         <v>64</v>
       </c>
       <c r="F84" s="9"/>
-      <c r="G84" s="12">
+      <c r="G84" s="11">
         <v>174</v>
       </c>
       <c r="H84" s="21">
-        <v>3.1</v>
-      </c>
-      <c r="I84" s="12"/>
+        <v>2.1</v>
+      </c>
+      <c r="I84" s="11"/>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="9" t="s">
@@ -5906,13 +5894,13 @@
         <v>64</v>
       </c>
       <c r="F85" s="9"/>
-      <c r="G85" s="12">
+      <c r="G85" s="11">
         <v>174</v>
       </c>
       <c r="H85" s="21">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I85" s="12"/>
+      <c r="I85" s="11"/>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="9" t="s">
@@ -5931,13 +5919,13 @@
         <v>65</v>
       </c>
       <c r="F86" s="9"/>
-      <c r="G86" s="12">
+      <c r="G86" s="11">
         <v>165</v>
       </c>
       <c r="H86" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I86" s="12"/>
+      <c r="I86" s="11"/>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="9" t="s">
@@ -5956,13 +5944,13 @@
         <v>65</v>
       </c>
       <c r="F87" s="9"/>
-      <c r="G87" s="12">
+      <c r="G87" s="11">
         <v>165</v>
       </c>
       <c r="H87" s="10">
         <v>2.5</v>
       </c>
-      <c r="I87" s="12"/>
+      <c r="I87" s="11"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="9" t="s">
@@ -5981,13 +5969,13 @@
         <v>65</v>
       </c>
       <c r="F88" s="9"/>
-      <c r="G88" s="12">
+      <c r="G88" s="11">
         <v>165</v>
       </c>
       <c r="H88" s="10">
         <v>2.6</v>
       </c>
-      <c r="I88" s="12"/>
+      <c r="I88" s="11"/>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="9" t="s">
@@ -6006,13 +5994,13 @@
         <v>68</v>
       </c>
       <c r="F89" s="9"/>
-      <c r="G89" s="12">
+      <c r="G89" s="11">
         <v>174</v>
       </c>
       <c r="H89" s="10">
         <v>2.6</v>
       </c>
-      <c r="I89" s="12"/>
+      <c r="I89" s="11"/>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="9" t="s">
@@ -6031,13 +6019,13 @@
         <v>78</v>
       </c>
       <c r="F90" s="9"/>
-      <c r="G90" s="12">
+      <c r="G90" s="11">
         <v>174</v>
       </c>
       <c r="H90" s="10">
         <v>2.7</v>
       </c>
-      <c r="I90" s="12"/>
+      <c r="I90" s="11"/>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="9" t="s">
@@ -6056,38 +6044,38 @@
         <v>82</v>
       </c>
       <c r="F91" s="9"/>
-      <c r="G91" s="12">
+      <c r="G91" s="11">
         <v>174</v>
       </c>
       <c r="H91" s="10">
         <v>2.8</v>
       </c>
-      <c r="I91" s="12"/>
+      <c r="I91" s="11"/>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="11" t="s">
         <v>39</v>
       </c>
       <c r="E92" s="10">
         <v>82</v>
       </c>
       <c r="F92" s="9"/>
-      <c r="G92" s="12">
-        <v>165</v>
-      </c>
-      <c r="H92" s="12">
+      <c r="G92" s="11">
+        <v>165</v>
+      </c>
+      <c r="H92" s="11">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I92" s="12"/>
+      <c r="I92" s="11"/>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="9" t="s">
@@ -6106,13 +6094,13 @@
         <v>92</v>
       </c>
       <c r="F93" s="9"/>
-      <c r="G93" s="12">
+      <c r="G93" s="11">
         <v>165</v>
       </c>
       <c r="H93" s="10">
         <v>2.9</v>
       </c>
-      <c r="I93" s="12"/>
+      <c r="I93" s="11"/>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="9" t="s">
@@ -6131,13 +6119,13 @@
         <v>82</v>
       </c>
       <c r="F94" s="9"/>
-      <c r="G94" s="12">
+      <c r="G94" s="11">
         <v>165</v>
       </c>
       <c r="H94" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I94" s="12"/>
+      <c r="I94" s="11"/>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="9" t="s">
@@ -6156,13 +6144,13 @@
         <v>75</v>
       </c>
       <c r="F95" s="9"/>
-      <c r="G95" s="12">
+      <c r="G95" s="11">
         <v>165</v>
       </c>
       <c r="H95" s="10">
         <v>2.7</v>
       </c>
-      <c r="I95" s="12"/>
+      <c r="I95" s="11"/>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="9" t="s">
@@ -6181,13 +6169,13 @@
         <v>70</v>
       </c>
       <c r="F96" s="9"/>
-      <c r="G96" s="12">
+      <c r="G96" s="11">
         <v>165</v>
       </c>
       <c r="H96" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I96" s="12"/>
+      <c r="I96" s="11"/>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="9" t="s">
@@ -6206,13 +6194,13 @@
         <v>94</v>
       </c>
       <c r="F97" s="9"/>
-      <c r="G97" s="12">
+      <c r="G97" s="11">
         <v>165</v>
       </c>
       <c r="H97" s="10">
         <v>2.6</v>
       </c>
-      <c r="I97" s="12"/>
+      <c r="I97" s="11"/>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="9" t="s">
@@ -6231,44 +6219,44 @@
         <v>72</v>
       </c>
       <c r="F98" s="9"/>
-      <c r="G98" s="12">
+      <c r="G98" s="11">
         <v>165</v>
       </c>
       <c r="H98" s="10">
         <v>2.9</v>
       </c>
-      <c r="I98" s="12"/>
+      <c r="I98" s="11"/>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="11" t="s">
         <v>144</v>
       </c>
       <c r="E99" s="10">
         <v>68</v>
       </c>
       <c r="F99" s="9"/>
-      <c r="G99" s="12">
-        <v>165</v>
-      </c>
-      <c r="H99" s="12">
+      <c r="G99" s="11">
+        <v>165</v>
+      </c>
+      <c r="H99" s="11">
         <v>2.7</v>
       </c>
-      <c r="I99" s="12"/>
+      <c r="I99" s="11"/>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="11" t="s">
         <v>248</v>
       </c>
       <c r="C100" s="10" t="s">
@@ -6281,13 +6269,13 @@
         <v>63</v>
       </c>
       <c r="F100" s="9"/>
-      <c r="G100" s="12">
+      <c r="G100" s="11">
         <v>165</v>
       </c>
       <c r="H100" s="10">
         <v>2.5</v>
       </c>
-      <c r="I100" s="12"/>
+      <c r="I100" s="11"/>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="9" t="s">
@@ -6306,13 +6294,13 @@
         <v>65</v>
       </c>
       <c r="F101" s="9"/>
-      <c r="G101" s="12">
+      <c r="G101" s="11">
         <v>165</v>
       </c>
       <c r="H101" s="10">
         <v>3.3</v>
       </c>
-      <c r="I101" s="12"/>
+      <c r="I101" s="11"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="9" t="s">
@@ -6331,13 +6319,13 @@
         <v>148</v>
       </c>
       <c r="F102" s="9"/>
-      <c r="G102" s="12">
+      <c r="G102" s="11">
         <v>165</v>
       </c>
       <c r="H102" s="22">
         <v>3.4</v>
       </c>
-      <c r="I102" s="12"/>
+      <c r="I102" s="11"/>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="9" t="s">
@@ -6356,13 +6344,13 @@
         <v>113</v>
       </c>
       <c r="F103" s="9"/>
-      <c r="G103" s="12">
+      <c r="G103" s="11">
         <v>165</v>
       </c>
       <c r="H103" s="22">
         <v>2.9</v>
       </c>
-      <c r="I103" s="12"/>
+      <c r="I103" s="11"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="9" t="s">
@@ -6381,13 +6369,13 @@
         <v>125</v>
       </c>
       <c r="F104" s="9"/>
-      <c r="G104" s="12">
+      <c r="G104" s="11">
         <v>165</v>
       </c>
       <c r="H104" s="22">
         <v>3.3</v>
       </c>
-      <c r="I104" s="12"/>
+      <c r="I104" s="11"/>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="9" t="s">
@@ -6406,13 +6394,13 @@
         <v>118</v>
       </c>
       <c r="F105" s="9"/>
-      <c r="G105" s="12">
+      <c r="G105" s="11">
         <v>165</v>
       </c>
       <c r="H105" s="22">
         <v>3.1</v>
       </c>
-      <c r="I105" s="12"/>
+      <c r="I105" s="11"/>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="9" t="s">
@@ -6431,13 +6419,13 @@
         <v>140</v>
       </c>
       <c r="F106" s="9"/>
-      <c r="G106" s="12">
+      <c r="G106" s="11">
         <v>165</v>
       </c>
       <c r="H106" s="22">
         <v>3.3</v>
       </c>
-      <c r="I106" s="12"/>
+      <c r="I106" s="11"/>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="9" t="s">
@@ -6450,19 +6438,19 @@
         <v>272</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" s="10">
         <v>79</v>
       </c>
       <c r="F107" s="9"/>
-      <c r="G107" s="12">
+      <c r="G107" s="11">
         <v>165</v>
       </c>
       <c r="H107" s="10">
         <v>2.5</v>
       </c>
-      <c r="I107" s="12"/>
+      <c r="I107" s="11"/>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="9" t="s">
@@ -6481,13 +6469,13 @@
         <v>70</v>
       </c>
       <c r="F108" s="9"/>
-      <c r="G108" s="12">
+      <c r="G108" s="11">
         <v>165</v>
       </c>
       <c r="H108" s="10">
         <v>2.8</v>
       </c>
-      <c r="I108" s="12"/>
+      <c r="I108" s="11"/>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="9" t="s">
@@ -6506,13 +6494,13 @@
         <v>69</v>
       </c>
       <c r="F109" s="9"/>
-      <c r="G109" s="12">
+      <c r="G109" s="11">
         <v>165</v>
       </c>
       <c r="H109" s="10">
         <v>2.7</v>
       </c>
-      <c r="I109" s="12"/>
+      <c r="I109" s="11"/>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="9" t="s">
@@ -6531,13 +6519,13 @@
         <v>88</v>
       </c>
       <c r="F110" s="9"/>
-      <c r="G110" s="12">
+      <c r="G110" s="11">
         <v>165</v>
       </c>
       <c r="H110" s="10">
         <v>3.4</v>
       </c>
-      <c r="I110" s="12"/>
+      <c r="I110" s="11"/>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="9" t="s">
@@ -6556,13 +6544,13 @@
         <v>60</v>
       </c>
       <c r="F111" s="9"/>
-      <c r="G111" s="12">
+      <c r="G111" s="11">
         <v>165</v>
       </c>
       <c r="H111" s="10">
         <v>3.2</v>
       </c>
-      <c r="I111" s="12"/>
+      <c r="I111" s="11"/>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="9" t="s">
@@ -6577,67 +6565,67 @@
       <c r="D112" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E112" s="12">
+      <c r="E112" s="11">
         <v>93</v>
       </c>
-      <c r="F112" s="13"/>
-      <c r="G112" s="12">
+      <c r="F112" s="12"/>
+      <c r="G112" s="11">
         <v>165</v>
       </c>
       <c r="H112" s="10">
         <v>2.9</v>
       </c>
-      <c r="I112" s="12"/>
+      <c r="I112" s="11"/>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E113" s="12">
+      <c r="E113" s="11">
         <v>72</v>
       </c>
-      <c r="F113" s="13"/>
-      <c r="G113" s="12">
-        <v>165</v>
-      </c>
-      <c r="H113" s="12">
+      <c r="F113" s="12"/>
+      <c r="G113" s="11">
+        <v>165</v>
+      </c>
+      <c r="H113" s="11">
         <v>2.6</v>
       </c>
-      <c r="I113" s="12"/>
+      <c r="I113" s="11"/>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D114" s="12" t="s">
+      <c r="D114" s="11" t="s">
         <v>148</v>
       </c>
       <c r="E114" s="10">
         <v>100</v>
       </c>
       <c r="F114" s="9"/>
-      <c r="G114" s="12">
-        <v>165</v>
-      </c>
-      <c r="H114" s="12">
+      <c r="G114" s="11">
+        <v>165</v>
+      </c>
+      <c r="H114" s="11">
         <v>2.9</v>
       </c>
-      <c r="I114" s="12"/>
+      <c r="I114" s="11"/>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="9" t="s">
@@ -6656,13 +6644,13 @@
         <v>76</v>
       </c>
       <c r="F115" s="9"/>
-      <c r="G115" s="12">
+      <c r="G115" s="11">
         <v>165</v>
       </c>
       <c r="H115" s="10">
         <v>2.6</v>
       </c>
-      <c r="I115" s="12"/>
+      <c r="I115" s="11"/>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="9" t="s">
@@ -6681,13 +6669,13 @@
         <v>61</v>
       </c>
       <c r="F116" s="9"/>
-      <c r="G116" s="12">
+      <c r="G116" s="11">
         <v>165</v>
       </c>
       <c r="H116" s="10">
         <v>2.8</v>
       </c>
-      <c r="I116" s="12"/>
+      <c r="I116" s="11"/>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="9" t="s">
@@ -6706,13 +6694,13 @@
         <v>70</v>
       </c>
       <c r="F117" s="9"/>
-      <c r="G117" s="12">
+      <c r="G117" s="11">
         <v>165</v>
       </c>
       <c r="H117" s="10">
         <v>2.4</v>
       </c>
-      <c r="I117" s="12"/>
+      <c r="I117" s="11"/>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="9" t="s">
@@ -6731,13 +6719,13 @@
         <v>76</v>
       </c>
       <c r="F118" s="9"/>
-      <c r="G118" s="12">
+      <c r="G118" s="11">
         <v>165</v>
       </c>
       <c r="H118" s="10">
         <v>3.2</v>
       </c>
-      <c r="I118" s="12"/>
+      <c r="I118" s="11"/>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="9" t="s">
@@ -6756,13 +6744,13 @@
         <v>76</v>
       </c>
       <c r="F119" s="9"/>
-      <c r="G119" s="12">
+      <c r="G119" s="11">
         <v>165</v>
       </c>
       <c r="H119" s="10">
         <v>3.2</v>
       </c>
-      <c r="I119" s="12"/>
+      <c r="I119" s="11"/>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="9" t="s">
@@ -6772,7 +6760,7 @@
         <v>302</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>148</v>
@@ -6781,13 +6769,13 @@
         <v>92</v>
       </c>
       <c r="F120" s="9"/>
-      <c r="G120" s="12">
+      <c r="G120" s="11">
         <v>165</v>
       </c>
       <c r="H120" s="10">
         <v>2.8</v>
       </c>
-      <c r="I120" s="12"/>
+      <c r="I120" s="11"/>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="9" t="s">
@@ -6806,13 +6794,13 @@
         <v>72</v>
       </c>
       <c r="F121" s="9"/>
-      <c r="G121" s="12">
+      <c r="G121" s="11">
         <v>165</v>
       </c>
       <c r="H121" s="10">
         <v>2.8</v>
       </c>
-      <c r="I121" s="12"/>
+      <c r="I121" s="11"/>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="9" t="s">
@@ -6822,7 +6810,7 @@
         <v>306</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>148</v>
@@ -6831,13 +6819,13 @@
         <v>92</v>
       </c>
       <c r="F122" s="9"/>
-      <c r="G122" s="12">
+      <c r="G122" s="11">
         <v>165</v>
       </c>
       <c r="H122" s="10">
         <v>2.5</v>
       </c>
-      <c r="I122" s="12"/>
+      <c r="I122" s="11"/>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="9" t="s">
@@ -6856,13 +6844,13 @@
         <v>68</v>
       </c>
       <c r="F123" s="9"/>
-      <c r="G123" s="12">
+      <c r="G123" s="11">
         <v>165</v>
       </c>
       <c r="H123" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I123" s="12"/>
+      <c r="I123" s="11"/>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="9" t="s">
@@ -6881,13 +6869,13 @@
         <v>105</v>
       </c>
       <c r="F124" s="9"/>
-      <c r="G124" s="12">
+      <c r="G124" s="11">
         <v>189</v>
       </c>
       <c r="H124" s="10">
         <v>3.5</v>
       </c>
-      <c r="I124" s="12"/>
+      <c r="I124" s="11"/>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="9" t="s">
@@ -6906,13 +6894,13 @@
         <v>92</v>
       </c>
       <c r="F125" s="9"/>
-      <c r="G125" s="12">
+      <c r="G125" s="11">
         <v>165</v>
       </c>
       <c r="H125" s="10">
         <v>2.9</v>
       </c>
-      <c r="I125" s="12"/>
+      <c r="I125" s="11"/>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="9" t="s">
@@ -6922,22 +6910,22 @@
         <v>318</v>
       </c>
       <c r="C126" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="10" t="s">
         <v>4</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="E126" s="10">
         <v>70</v>
       </c>
       <c r="F126" s="9"/>
-      <c r="G126" s="12">
+      <c r="G126" s="11">
         <v>165</v>
       </c>
       <c r="H126" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I126" s="12"/>
+      <c r="I126" s="11"/>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="9" t="s">
@@ -6956,13 +6944,13 @@
         <v>86</v>
       </c>
       <c r="F127" s="9"/>
-      <c r="G127" s="12">
+      <c r="G127" s="11">
         <v>165</v>
       </c>
       <c r="H127" s="10">
         <v>2.8</v>
       </c>
-      <c r="I127" s="12"/>
+      <c r="I127" s="11"/>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="9" t="s">
@@ -6975,19 +6963,19 @@
         <v>290</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E128" s="10">
         <v>84</v>
       </c>
       <c r="F128" s="9"/>
-      <c r="G128" s="12">
+      <c r="G128" s="11">
         <v>165</v>
       </c>
       <c r="H128" s="10">
         <v>2.7</v>
       </c>
-      <c r="I128" s="12"/>
+      <c r="I128" s="11"/>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="9" t="s">
@@ -7006,13 +6994,13 @@
         <v>92</v>
       </c>
       <c r="F129" s="9"/>
-      <c r="G129" s="12">
+      <c r="G129" s="11">
         <v>165</v>
       </c>
       <c r="H129" s="10">
         <v>3.2</v>
       </c>
-      <c r="I129" s="12"/>
+      <c r="I129" s="11"/>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="9" t="s">
@@ -7031,13 +7019,13 @@
         <v>70</v>
       </c>
       <c r="F130" s="9"/>
-      <c r="G130" s="12">
+      <c r="G130" s="11">
         <v>165</v>
       </c>
       <c r="H130" s="24">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I130" s="12"/>
+      <c r="I130" s="11"/>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="9" t="s">
@@ -7047,7 +7035,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>148</v>
@@ -7056,13 +7044,13 @@
         <v>90</v>
       </c>
       <c r="F131" s="9"/>
-      <c r="G131" s="12">
+      <c r="G131" s="11">
         <v>165</v>
       </c>
       <c r="H131" s="24">
         <v>2.5</v>
       </c>
-      <c r="I131" s="12"/>
+      <c r="I131" s="11"/>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="9" t="s">
@@ -7081,13 +7069,13 @@
         <v>120</v>
       </c>
       <c r="F132" s="9"/>
-      <c r="G132" s="12">
+      <c r="G132" s="11">
         <v>165</v>
       </c>
       <c r="H132" s="24">
         <v>2.9</v>
       </c>
-      <c r="I132" s="12"/>
+      <c r="I132" s="11"/>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="9" t="s">
@@ -7106,13 +7094,13 @@
         <v>98</v>
       </c>
       <c r="F133" s="9"/>
-      <c r="G133" s="12">
+      <c r="G133" s="11">
         <v>165</v>
       </c>
       <c r="H133" s="24">
         <v>2.9</v>
       </c>
-      <c r="I133" s="12"/>
+      <c r="I133" s="11"/>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="9" t="s">
@@ -7129,13 +7117,13 @@
       </c>
       <c r="E134" s="25"/>
       <c r="F134" s="9"/>
-      <c r="G134" s="12">
+      <c r="G134" s="11">
         <v>165</v>
       </c>
       <c r="H134" s="25">
         <v>2.8</v>
       </c>
-      <c r="I134" s="12"/>
+      <c r="I134" s="11"/>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="9" t="s">
@@ -7154,13 +7142,13 @@
         <v>88</v>
       </c>
       <c r="F135" s="9"/>
-      <c r="G135" s="12">
+      <c r="G135" s="11">
         <v>165</v>
       </c>
       <c r="H135" s="26">
         <v>2.6</v>
       </c>
-      <c r="I135" s="12"/>
+      <c r="I135" s="11"/>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="9" t="s">
@@ -7179,13 +7167,13 @@
         <v>88</v>
       </c>
       <c r="F136" s="9"/>
-      <c r="G136" s="12">
+      <c r="G136" s="11">
         <v>165</v>
       </c>
       <c r="H136" s="26">
         <v>2.7</v>
       </c>
-      <c r="I136" s="12"/>
+      <c r="I136" s="11"/>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="9" t="s">
@@ -7204,13 +7192,13 @@
         <v>103</v>
       </c>
       <c r="F137" s="9"/>
-      <c r="G137" s="12">
+      <c r="G137" s="11">
         <v>165</v>
       </c>
       <c r="H137" s="26">
         <v>2.7</v>
       </c>
-      <c r="I137" s="12"/>
+      <c r="I137" s="11"/>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="9" t="s">
@@ -7229,13 +7217,13 @@
         <v>102</v>
       </c>
       <c r="F138" s="9"/>
-      <c r="G138" s="12">
+      <c r="G138" s="11">
         <v>165</v>
       </c>
       <c r="H138" s="26">
         <v>2.8</v>
       </c>
-      <c r="I138" s="12"/>
+      <c r="I138" s="11"/>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="9" t="s">
@@ -7254,13 +7242,13 @@
         <v>110</v>
       </c>
       <c r="F139" s="9"/>
-      <c r="G139" s="12">
+      <c r="G139" s="11">
         <v>165</v>
       </c>
       <c r="H139" s="26">
         <v>3</v>
       </c>
-      <c r="I139" s="12"/>
+      <c r="I139" s="11"/>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="9" t="s">
@@ -7279,13 +7267,13 @@
         <v>113</v>
       </c>
       <c r="F140" s="9"/>
-      <c r="G140" s="12">
+      <c r="G140" s="11">
         <v>165</v>
       </c>
       <c r="H140" s="26">
         <v>3.1</v>
       </c>
-      <c r="I140" s="12"/>
+      <c r="I140" s="11"/>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="9" t="s">
@@ -7304,38 +7292,38 @@
         <v>95</v>
       </c>
       <c r="F141" s="9"/>
-      <c r="G141" s="12">
+      <c r="G141" s="11">
         <v>165</v>
       </c>
       <c r="H141" s="26">
         <v>2.8</v>
       </c>
-      <c r="I141" s="12"/>
+      <c r="I141" s="11"/>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="B142" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="C142" s="12" t="s">
+      <c r="C142" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="D142" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E142" s="12">
+      <c r="E142" s="11">
         <v>72</v>
       </c>
       <c r="F142" s="9"/>
-      <c r="G142" s="12">
-        <v>165</v>
-      </c>
-      <c r="H142" s="12">
+      <c r="G142" s="11">
+        <v>165</v>
+      </c>
+      <c r="H142" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I142" s="12"/>
+      <c r="I142" s="11"/>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="9" t="s">
@@ -7354,13 +7342,13 @@
         <v>57</v>
       </c>
       <c r="F143" s="9"/>
-      <c r="G143" s="12">
+      <c r="G143" s="11">
         <v>165</v>
       </c>
       <c r="H143" s="10">
         <v>2.5</v>
       </c>
-      <c r="I143" s="12"/>
+      <c r="I143" s="11"/>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="9" t="s">
@@ -7379,13 +7367,13 @@
         <v>62</v>
       </c>
       <c r="F144" s="9"/>
-      <c r="G144" s="12">
+      <c r="G144" s="11">
         <v>165</v>
       </c>
       <c r="H144" s="10">
         <v>2.6</v>
       </c>
-      <c r="I144" s="12"/>
+      <c r="I144" s="11"/>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="9" t="s">
@@ -7404,13 +7392,13 @@
         <v>62</v>
       </c>
       <c r="F145" s="9"/>
-      <c r="G145" s="12">
+      <c r="G145" s="11">
         <v>165</v>
       </c>
       <c r="H145" s="10">
         <v>2.5</v>
       </c>
-      <c r="I145" s="12"/>
+      <c r="I145" s="11"/>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="9" t="s">
@@ -7429,13 +7417,13 @@
         <v>62</v>
       </c>
       <c r="F146" s="9"/>
-      <c r="G146" s="12">
+      <c r="G146" s="11">
         <v>165</v>
       </c>
       <c r="H146" s="10">
         <v>2.6</v>
       </c>
-      <c r="I146" s="12"/>
+      <c r="I146" s="11"/>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="9" t="s">
@@ -7454,38 +7442,38 @@
         <v>62</v>
       </c>
       <c r="F147" s="9"/>
-      <c r="G147" s="12">
+      <c r="G147" s="11">
         <v>165</v>
       </c>
       <c r="H147" s="10">
         <v>2.5</v>
       </c>
-      <c r="I147" s="12"/>
+      <c r="I147" s="11"/>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="B148" s="12" t="s">
+      <c r="B148" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="C148" s="12" t="s">
+      <c r="C148" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D148" s="12" t="s">
+      <c r="D148" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E148" s="12">
+      <c r="E148" s="11">
         <v>70</v>
       </c>
-      <c r="F148" s="13"/>
-      <c r="G148" s="12">
-        <v>165</v>
-      </c>
-      <c r="H148" s="12">
+      <c r="F148" s="12"/>
+      <c r="G148" s="11">
+        <v>165</v>
+      </c>
+      <c r="H148" s="11">
         <v>2.5</v>
       </c>
-      <c r="I148" s="12"/>
+      <c r="I148" s="11"/>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="9" t="s">
@@ -7504,13 +7492,13 @@
         <v>95</v>
       </c>
       <c r="F149" s="9"/>
-      <c r="G149" s="12">
+      <c r="G149" s="11">
         <v>165</v>
       </c>
       <c r="H149" s="10">
         <v>3</v>
       </c>
-      <c r="I149" s="12"/>
+      <c r="I149" s="11"/>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="9" t="s">
@@ -7529,92 +7517,92 @@
         <v>97</v>
       </c>
       <c r="F150" s="9"/>
-      <c r="G150" s="12">
+      <c r="G150" s="11">
         <v>165</v>
       </c>
       <c r="H150" s="10">
         <v>3.3</v>
       </c>
-      <c r="I150" s="12"/>
+      <c r="I150" s="11"/>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B151" s="12" t="s">
+      <c r="B151" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C151" s="12" t="s">
+      <c r="C151" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="D151" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E151" s="12">
+      <c r="E151" s="11">
         <v>72</v>
       </c>
       <c r="F151" s="9"/>
-      <c r="G151" s="12">
-        <v>165</v>
-      </c>
-      <c r="H151" s="12">
+      <c r="G151" s="11">
+        <v>165</v>
+      </c>
+      <c r="H151" s="11">
         <v>2.5</v>
       </c>
-      <c r="I151" s="12"/>
+      <c r="I151" s="11"/>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="D152" s="14" t="s">
+      <c r="D152" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E152" s="14">
+      <c r="E152" s="13">
         <v>90</v>
       </c>
       <c r="F152" s="9">
         <v>130</v>
       </c>
-      <c r="G152" s="12">
+      <c r="G152" s="11">
         <v>208</v>
       </c>
-      <c r="H152" s="14">
+      <c r="H152" s="13">
         <v>2.8</v>
       </c>
-      <c r="I152" s="12"/>
+      <c r="I152" s="11"/>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B153" s="14" t="s">
+      <c r="B153" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="14" t="s">
+      <c r="C153" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="D153" s="14" t="s">
+      <c r="D153" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E153" s="14">
+      <c r="E153" s="13">
         <v>100</v>
       </c>
       <c r="F153" s="9">
         <v>150</v>
       </c>
-      <c r="G153" s="12">
+      <c r="G153" s="11">
         <v>216</v>
       </c>
-      <c r="H153" s="14">
-        <v>3.7</v>
-      </c>
-      <c r="I153" s="12"/>
+      <c r="H153" s="13">
+        <v>3.6</v>
+      </c>
+      <c r="I153" s="11"/>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="9" t="s">
@@ -7635,13 +7623,13 @@
       <c r="F154" s="9">
         <v>130</v>
       </c>
-      <c r="G154" s="12">
+      <c r="G154" s="11">
         <v>208</v>
       </c>
       <c r="H154" s="10">
         <v>3.5</v>
       </c>
-      <c r="I154" s="12"/>
+      <c r="I154" s="11"/>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="9" t="s">
@@ -7662,13 +7650,13 @@
       <c r="F155" s="9">
         <v>135</v>
       </c>
-      <c r="G155" s="12">
+      <c r="G155" s="11">
         <v>220</v>
       </c>
       <c r="H155" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="I155" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="I155" s="11"/>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="9" t="s">
@@ -7689,67 +7677,67 @@
       <c r="F156" s="9">
         <v>150</v>
       </c>
-      <c r="G156" s="12">
+      <c r="G156" s="11">
         <v>215</v>
       </c>
       <c r="H156" s="10">
         <v>4.5</v>
       </c>
-      <c r="I156" s="12"/>
+      <c r="I156" s="11"/>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="B157" s="14" t="s">
+      <c r="B157" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="C157" s="14" t="s">
+      <c r="C157" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="D157" s="14" t="s">
+      <c r="D157" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E157" s="14">
+      <c r="E157" s="13">
         <v>92</v>
       </c>
       <c r="F157" s="9">
         <v>135</v>
       </c>
-      <c r="G157" s="12">
+      <c r="G157" s="11">
         <v>208</v>
       </c>
-      <c r="H157" s="14">
+      <c r="H157" s="13">
         <v>3.1</v>
       </c>
-      <c r="I157" s="12"/>
+      <c r="I157" s="11"/>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="B158" s="28" t="s">
+      <c r="B158" s="27" t="s">
         <v>403</v>
       </c>
-      <c r="C158" s="28" t="s">
+      <c r="C158" s="27" t="s">
         <v>404</v>
       </c>
-      <c r="D158" s="28" t="s">
+      <c r="D158" s="27" t="s">
         <v>393</v>
       </c>
-      <c r="E158" s="28">
+      <c r="E158" s="27">
         <v>94</v>
       </c>
       <c r="F158" s="9">
         <v>136</v>
       </c>
-      <c r="G158" s="12">
+      <c r="G158" s="11">
         <v>225</v>
       </c>
-      <c r="H158" s="28">
+      <c r="H158" s="27">
         <v>3.6</v>
       </c>
-      <c r="I158" s="12"/>
+      <c r="I158" s="11"/>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="9" t="s">
@@ -7768,13 +7756,13 @@
         <v>120</v>
       </c>
       <c r="F159" s="9"/>
-      <c r="G159" s="12">
+      <c r="G159" s="11">
         <v>199</v>
       </c>
-      <c r="H159" s="29">
+      <c r="H159" s="28">
         <v>3.4</v>
       </c>
-      <c r="I159" s="12"/>
+      <c r="I159" s="11"/>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="9" t="s">
@@ -7793,20 +7781,20 @@
         <v>85</v>
       </c>
       <c r="F160" s="9"/>
-      <c r="G160" s="12">
+      <c r="G160" s="11">
         <v>220</v>
       </c>
       <c r="H160" s="10">
         <v>5.5</v>
       </c>
-      <c r="I160" s="12"/>
+      <c r="I160" s="11"/>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="9" t="s">
         <v>412</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>413</v>
@@ -7817,16 +7805,16 @@
       <c r="E161" s="22">
         <v>104</v>
       </c>
-      <c r="F161" s="27">
+      <c r="F161" s="29">
         <v>150</v>
       </c>
-      <c r="G161" s="12">
+      <c r="G161" s="11">
         <v>208</v>
       </c>
       <c r="H161" s="22">
         <v>2.9</v>
       </c>
-      <c r="I161" s="12"/>
+      <c r="I161" s="11"/>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="9" t="s">
@@ -7844,16 +7832,16 @@
       <c r="E162" s="22">
         <v>117</v>
       </c>
-      <c r="F162" s="27">
+      <c r="F162" s="29">
         <v>175</v>
       </c>
-      <c r="G162" s="12">
+      <c r="G162" s="11">
         <v>208</v>
       </c>
       <c r="H162" s="22">
         <v>4.2</v>
       </c>
-      <c r="I162" s="12"/>
+      <c r="I162" s="11"/>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="9" t="s">
@@ -7871,23 +7859,23 @@
       <c r="E163" s="22">
         <v>117</v>
       </c>
-      <c r="F163" s="27">
+      <c r="F163" s="29">
         <v>175</v>
       </c>
-      <c r="G163" s="12">
+      <c r="G163" s="11">
         <v>208</v>
       </c>
       <c r="H163" s="22">
-        <v>5</v>
-      </c>
-      <c r="I163" s="12"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I163" s="11"/>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="9" t="s">
         <v>421</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>422</v>
@@ -7898,26 +7886,26 @@
       <c r="E164" s="22">
         <v>110</v>
       </c>
-      <c r="F164" s="27">
-        <v>165</v>
-      </c>
-      <c r="G164" s="12">
+      <c r="F164" s="29">
+        <v>165</v>
+      </c>
+      <c r="G164" s="11">
         <v>208</v>
       </c>
       <c r="H164" s="22">
-        <v>3.3</v>
-      </c>
-      <c r="I164" s="12"/>
+        <v>3.2</v>
+      </c>
+      <c r="I164" s="11"/>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="9" t="s">
         <v>423</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>414</v>
@@ -7925,16 +7913,16 @@
       <c r="E165" s="22">
         <v>108</v>
       </c>
-      <c r="F165" s="27">
+      <c r="F165" s="29">
         <v>158</v>
       </c>
-      <c r="G165" s="12">
+      <c r="G165" s="11">
         <v>208</v>
       </c>
       <c r="H165" s="22">
         <v>3</v>
       </c>
-      <c r="I165" s="12"/>
+      <c r="I165" s="11"/>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="9" t="s">
@@ -7947,20 +7935,20 @@
       <c r="F166" s="30"/>
       <c r="G166" s="30"/>
       <c r="H166" s="30"/>
-      <c r="I166" s="12"/>
+      <c r="I166" s="11"/>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="9" t="s">
         <v>425</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -7972,22 +7960,22 @@
         <v>220</v>
       </c>
       <c r="H167" s="18">
-        <v>4.3</v>
-      </c>
-      <c r="I167" s="12"/>
+        <v>4.2</v>
+      </c>
+      <c r="I167" s="11"/>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="9" t="s">
         <v>426</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>723</v>
+        <v>417</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -7999,16 +7987,16 @@
         <v>208</v>
       </c>
       <c r="H168" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="I168" s="12"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I168" s="11"/>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" s="31" t="s">
         <v>427</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>428</v>
@@ -8026,7 +8014,7 @@
         <v>208</v>
       </c>
       <c r="H169" s="18">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I169" s="32"/>
     </row>
@@ -8035,7 +8023,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>431</v>
@@ -8062,7 +8050,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>238</v>
@@ -8080,7 +8068,7 @@
         <v>215</v>
       </c>
       <c r="H171" s="32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I171" s="32"/>
     </row>
@@ -8116,7 +8104,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>436</v>
@@ -8143,7 +8131,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>439</v>
@@ -8170,7 +8158,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8188,7 +8176,7 @@
         <v>215</v>
       </c>
       <c r="H175" s="32">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I175" s="32"/>
     </row>
@@ -8215,7 +8203,7 @@
         <v>215</v>
       </c>
       <c r="H176" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I176" s="32"/>
     </row>
@@ -8242,7 +8230,7 @@
         <v>215</v>
       </c>
       <c r="H177" s="18">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I177" s="32"/>
     </row>
@@ -8251,7 +8239,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>420</v>
@@ -8269,7 +8257,7 @@
         <v>208</v>
       </c>
       <c r="H178" s="18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I178" s="32"/>
     </row>
@@ -8296,7 +8284,7 @@
         <v>208</v>
       </c>
       <c r="H179" s="18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I179" s="32"/>
     </row>
@@ -8305,7 +8293,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>451</v>
@@ -8323,7 +8311,7 @@
         <v>208</v>
       </c>
       <c r="H180" s="18">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I180" s="32"/>
     </row>
@@ -8332,7 +8320,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>445</v>
@@ -8352,14 +8340,14 @@
       <c r="H181" s="18">
         <v>4.5</v>
       </c>
-      <c r="I181" s="12"/>
+      <c r="I181" s="11"/>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="9" t="s">
         <v>453</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>309</v>
@@ -8373,20 +8361,20 @@
       <c r="F182" s="9">
         <v>168</v>
       </c>
-      <c r="G182" s="12">
+      <c r="G182" s="11">
         <v>215</v>
       </c>
       <c r="H182" s="34">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I182" s="12"/>
+      <c r="I182" s="11"/>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="9" t="s">
         <v>455</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>309</v>
@@ -8400,13 +8388,13 @@
       <c r="F183" s="9">
         <v>168</v>
       </c>
-      <c r="G183" s="12">
+      <c r="G183" s="11">
         <v>215</v>
       </c>
       <c r="H183" s="34">
         <v>4.7</v>
       </c>
-      <c r="I183" s="12"/>
+      <c r="I183" s="11"/>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="9" t="s">
@@ -8440,13 +8428,13 @@
         <v>460</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>737</v>
+        <v>445</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>738</v>
+        <v>429</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8458,16 +8446,16 @@
         <v>215</v>
       </c>
       <c r="H185" s="18">
-        <v>3.7</v>
-      </c>
-      <c r="I185" s="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="I185" s="11"/>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="9" t="s">
         <v>461</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>309</v>
@@ -8481,23 +8469,23 @@
       <c r="F186" s="9">
         <v>168</v>
       </c>
-      <c r="G186" s="12">
+      <c r="G186" s="11">
         <v>215</v>
       </c>
       <c r="H186" s="34">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I186" s="12"/>
+      <c r="I186" s="11"/>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>442</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>741</v>
+        <v>238</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>437</v>
@@ -8512,22 +8500,22 @@
         <v>215</v>
       </c>
       <c r="H187" s="18">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I187" s="12"/>
+        <v>4.5</v>
+      </c>
+      <c r="I187" s="11"/>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="9" t="s">
         <v>462</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>743</v>
+        <v>272</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8539,16 +8527,16 @@
         <v>215</v>
       </c>
       <c r="H188" s="18">
-        <v>3.9</v>
-      </c>
-      <c r="I188" s="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="I188" s="11"/>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="9" t="s">
         <v>463</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>445</v>
@@ -8568,44 +8556,44 @@
       <c r="H189" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I189" s="12"/>
+      <c r="I189" s="11"/>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="9" t="s">
         <v>464</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>747</v>
+        <v>875</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>748</v>
-      </c>
-      <c r="E190" s="12">
-        <v>177</v>
-      </c>
-      <c r="F190" s="13">
-        <v>263</v>
-      </c>
-      <c r="G190" s="12">
-        <v>225</v>
+        <v>738</v>
+      </c>
+      <c r="E190" s="11">
+        <v>152</v>
+      </c>
+      <c r="F190" s="12">
+        <v>245</v>
+      </c>
+      <c r="G190" s="11">
+        <v>215</v>
       </c>
       <c r="H190" s="10">
-        <v>5.4</v>
-      </c>
-      <c r="I190" s="12"/>
+        <v>5.2</v>
+      </c>
+      <c r="I190" s="11"/>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="9" t="s">
         <v>465</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>741</v>
+        <v>238</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>437</v>
@@ -8620,60 +8608,60 @@
         <v>215</v>
       </c>
       <c r="H191" s="32">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I191" s="12"/>
+        <v>4.5</v>
+      </c>
+      <c r="I191" s="11"/>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="B192" s="28"/>
-      <c r="C192" s="28"/>
-      <c r="D192" s="28"/>
-      <c r="E192" s="28"/>
-      <c r="F192" s="27"/>
+      <c r="B192" s="27"/>
+      <c r="C192" s="27"/>
+      <c r="D192" s="27"/>
+      <c r="E192" s="27"/>
+      <c r="F192" s="29"/>
       <c r="G192" s="20"/>
-      <c r="H192" s="28"/>
-      <c r="I192" s="12"/>
+      <c r="H192" s="27"/>
+      <c r="I192" s="11"/>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="B193" s="28"/>
-      <c r="C193" s="28"/>
-      <c r="D193" s="28"/>
-      <c r="E193" s="40"/>
-      <c r="F193" s="27"/>
-      <c r="G193" s="41"/>
-      <c r="H193" s="40"/>
+      <c r="B193" s="27"/>
+      <c r="C193" s="27"/>
+      <c r="D193" s="27"/>
+      <c r="E193" s="39"/>
+      <c r="F193" s="29"/>
+      <c r="G193" s="40"/>
+      <c r="H193" s="39"/>
       <c r="I193" s="37"/>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="B194" s="42" t="s">
-        <v>749</v>
-      </c>
-      <c r="C194" s="43" t="s">
-        <v>750</v>
-      </c>
-      <c r="D194" s="44" t="s">
+      <c r="B194" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="C194" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="D194" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="E194" s="42">
+      <c r="E194" s="41">
         <v>138</v>
       </c>
-      <c r="F194" s="45">
+      <c r="F194" s="44">
         <v>215</v>
       </c>
-      <c r="G194" s="43">
+      <c r="G194" s="42">
         <v>225</v>
       </c>
-      <c r="H194" s="42">
-        <v>4.3</v>
+      <c r="H194" s="41">
+        <v>4.2</v>
       </c>
       <c r="I194" s="37"/>
     </row>
@@ -8681,25 +8669,25 @@
       <c r="A195" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="B195" s="42" t="s">
-        <v>751</v>
-      </c>
-      <c r="C195" s="43" t="s">
+      <c r="B195" s="41" t="s">
+        <v>740</v>
+      </c>
+      <c r="C195" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="D195" s="44" t="s">
+      <c r="D195" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E195" s="42">
+      <c r="E195" s="41">
         <v>110</v>
       </c>
-      <c r="F195" s="45">
-        <v>165</v>
-      </c>
-      <c r="G195" s="43">
+      <c r="F195" s="44">
+        <v>165</v>
+      </c>
+      <c r="G195" s="42">
         <v>208</v>
       </c>
-      <c r="H195" s="42">
+      <c r="H195" s="41">
         <v>4</v>
       </c>
       <c r="I195" s="37"/>
@@ -8708,52 +8696,52 @@
       <c r="A196" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="B196" s="46" t="s">
-        <v>752</v>
-      </c>
-      <c r="C196" s="46" t="s">
-        <v>753</v>
-      </c>
-      <c r="D196" s="46" t="s">
+      <c r="B196" s="45" t="s">
+        <v>741</v>
+      </c>
+      <c r="C196" s="45" t="s">
+        <v>742</v>
+      </c>
+      <c r="D196" s="45" t="s">
         <v>472</v>
       </c>
-      <c r="E196" s="46">
+      <c r="E196" s="45">
         <v>105</v>
       </c>
       <c r="F196" s="36">
         <v>155</v>
       </c>
-      <c r="G196" s="12">
+      <c r="G196" s="11">
         <v>215</v>
       </c>
-      <c r="H196" s="46">
-        <v>4.2</v>
-      </c>
-      <c r="I196" s="12"/>
+      <c r="H196" s="45">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I196" s="11"/>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="B197" s="46" t="s">
-        <v>754</v>
-      </c>
-      <c r="C197" s="46" t="s">
-        <v>755</v>
-      </c>
-      <c r="D197" s="46" t="s">
+      <c r="B197" s="45" t="s">
+        <v>743</v>
+      </c>
+      <c r="C197" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="D197" s="45" t="s">
         <v>386</v>
       </c>
-      <c r="E197" s="46">
+      <c r="E197" s="45">
         <v>100</v>
       </c>
-      <c r="F197" s="27">
+      <c r="F197" s="29">
         <v>150</v>
       </c>
-      <c r="G197" s="12">
+      <c r="G197" s="11">
         <v>215</v>
       </c>
-      <c r="H197" s="46">
+      <c r="H197" s="45">
         <v>3.7</v>
       </c>
       <c r="I197" s="37"/>
@@ -8762,25 +8750,25 @@
       <c r="A198" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B198" s="46" t="s">
-        <v>756</v>
-      </c>
-      <c r="C198" s="46" t="s">
+      <c r="B198" s="45" t="s">
+        <v>744</v>
+      </c>
+      <c r="C198" s="45" t="s">
         <v>475</v>
       </c>
-      <c r="D198" s="46" t="s">
+      <c r="D198" s="45" t="s">
         <v>476</v>
       </c>
-      <c r="E198" s="46">
+      <c r="E198" s="45">
         <v>129</v>
       </c>
-      <c r="F198" s="39">
+      <c r="F198" s="46">
         <v>183</v>
       </c>
-      <c r="G198" s="12">
+      <c r="G198" s="11">
         <v>215</v>
       </c>
-      <c r="H198" s="46">
+      <c r="H198" s="45">
         <v>4</v>
       </c>
       <c r="I198" s="37"/>
@@ -8789,26 +8777,26 @@
       <c r="A199" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="B199" s="46" t="s">
-        <v>757</v>
-      </c>
-      <c r="C199" s="46" t="s">
-        <v>758</v>
-      </c>
-      <c r="D199" s="46" t="s">
-        <v>759</v>
-      </c>
-      <c r="E199" s="46">
+      <c r="B199" s="45" t="s">
+        <v>745</v>
+      </c>
+      <c r="C199" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="D199" s="45" t="s">
+        <v>746</v>
+      </c>
+      <c r="E199" s="45">
         <v>95</v>
       </c>
-      <c r="F199" s="27">
+      <c r="F199" s="29">
         <v>145</v>
       </c>
-      <c r="G199" s="12">
+      <c r="G199" s="11">
         <v>215</v>
       </c>
-      <c r="H199" s="46">
-        <v>3.7</v>
+      <c r="H199" s="45">
+        <v>3.8</v>
       </c>
       <c r="I199" s="37"/>
     </row>
@@ -8834,7 +8822,7 @@
       <c r="D201" s="10"/>
       <c r="E201" s="10"/>
       <c r="F201" s="9"/>
-      <c r="G201" s="12"/>
+      <c r="G201" s="11"/>
       <c r="H201" s="10"/>
       <c r="I201" s="37"/>
     </row>
@@ -8847,7 +8835,7 @@
       <c r="D202" s="10"/>
       <c r="E202" s="10"/>
       <c r="F202" s="36"/>
-      <c r="G202" s="12"/>
+      <c r="G202" s="11"/>
       <c r="H202" s="10"/>
       <c r="I202" s="37"/>
     </row>
@@ -8860,7 +8848,7 @@
       <c r="D203" s="10"/>
       <c r="E203" s="10"/>
       <c r="F203" s="36"/>
-      <c r="G203" s="12"/>
+      <c r="G203" s="11"/>
       <c r="H203" s="10"/>
       <c r="I203" s="37"/>
     </row>
@@ -8914,7 +8902,7 @@
       <c r="H205" s="24">
         <v>3.6</v>
       </c>
-      <c r="I205" s="12"/>
+      <c r="I205" s="11"/>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="9" t="s">
@@ -8941,24 +8929,24 @@
       <c r="H206" s="24">
         <v>3</v>
       </c>
-      <c r="I206" s="12"/>
+      <c r="I206" s="11"/>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="B207" s="28" t="s">
+      <c r="B207" s="27" t="s">
         <v>494</v>
       </c>
       <c r="C207" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D207" s="12" t="s">
+      <c r="D207" s="11" t="s">
         <v>275</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="36"/>
-      <c r="G207" s="12">
+      <c r="G207" s="11">
         <v>165</v>
       </c>
       <c r="H207" s="10">
@@ -8970,11 +8958,11 @@
       <c r="A208" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="B208" s="28" t="s">
+      <c r="B208" s="27" t="s">
         <v>496</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -8985,13 +8973,13 @@
       <c r="F208" s="36">
         <v>150</v>
       </c>
-      <c r="G208" s="12">
+      <c r="G208" s="11">
         <v>170</v>
       </c>
       <c r="H208" s="10">
         <v>3.8</v>
       </c>
-      <c r="I208" s="12"/>
+      <c r="I208" s="11"/>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="9" t="s">
@@ -9008,7 +8996,7 @@
       </c>
       <c r="E209" s="10"/>
       <c r="F209" s="36"/>
-      <c r="G209" s="12">
+      <c r="G209" s="11">
         <v>165</v>
       </c>
       <c r="H209" s="10">
@@ -9025,7 +9013,7 @@
       <c r="D210" s="10"/>
       <c r="E210" s="10"/>
       <c r="F210" s="36"/>
-      <c r="G210" s="12"/>
+      <c r="G210" s="11"/>
       <c r="H210" s="10"/>
       <c r="I210" s="37"/>
     </row>
@@ -9037,7 +9025,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9046,11 +9034,11 @@
         <v>90</v>
       </c>
       <c r="F211" s="36"/>
-      <c r="G211" s="12">
+      <c r="G211" s="11">
         <v>174</v>
       </c>
       <c r="H211" s="10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I211" s="37"/>
     </row>
@@ -9059,10 +9047,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>144</v>
@@ -9071,7 +9059,7 @@
         <v>62</v>
       </c>
       <c r="F212" s="36"/>
-      <c r="G212" s="12">
+      <c r="G212" s="11">
         <v>175</v>
       </c>
       <c r="H212" s="35">
@@ -9098,11 +9086,11 @@
       <c r="F213" s="36">
         <v>58</v>
       </c>
-      <c r="G213" s="12">
+      <c r="G213" s="11">
         <v>178</v>
       </c>
       <c r="H213" s="10">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I213" s="37"/>
     </row>
@@ -9114,7 +9102,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>144</v>
@@ -9123,7 +9111,7 @@
         <v>65</v>
       </c>
       <c r="F214" s="36"/>
-      <c r="G214" s="12">
+      <c r="G214" s="11">
         <v>175</v>
       </c>
       <c r="H214" s="10">
@@ -9161,7 +9149,7 @@
         <v>69</v>
       </c>
       <c r="F216" s="36"/>
-      <c r="G216" s="12">
+      <c r="G216" s="11">
         <v>170</v>
       </c>
       <c r="H216" s="10">
@@ -9180,7 +9168,7 @@
       <c r="F217" s="30"/>
       <c r="G217" s="30"/>
       <c r="H217" s="30"/>
-      <c r="I217" s="12"/>
+      <c r="I217" s="11"/>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="9" t="s">
@@ -9188,10 +9176,10 @@
       </c>
       <c r="B218" s="10"/>
       <c r="C218" s="10"/>
-      <c r="D218" s="28"/>
+      <c r="D218" s="27"/>
       <c r="E218" s="10"/>
       <c r="F218" s="36"/>
-      <c r="G218" s="12"/>
+      <c r="G218" s="11"/>
       <c r="H218" s="10"/>
       <c r="I218" s="37"/>
     </row>
@@ -9227,40 +9215,42 @@
         <v>519</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>765</v>
+        <v>876</v>
       </c>
       <c r="D220" s="49" t="s">
         <v>520</v>
       </c>
       <c r="E220" s="10">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F220" s="9">
-        <v>173</v>
-      </c>
-      <c r="G220" s="12">
+        <v>170</v>
+      </c>
+      <c r="G220" s="11">
         <v>215</v>
       </c>
       <c r="H220" s="10">
         <v>3.5</v>
       </c>
-      <c r="I220" s="12"/>
+      <c r="I220" s="11" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="9" t="s">
         <v>521</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>709</v>
+        <v>4</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9268,14 +9258,14 @@
       <c r="F221" s="9">
         <v>155</v>
       </c>
-      <c r="G221" s="12">
+      <c r="G221" s="11">
         <v>208</v>
       </c>
       <c r="H221" s="10">
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9283,13 +9273,13 @@
         <v>522</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>771</v>
+        <v>520</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9297,7 +9287,7 @@
       <c r="F222" s="9">
         <v>165</v>
       </c>
-      <c r="G222" s="12">
+      <c r="G222" s="11">
         <v>215</v>
       </c>
       <c r="H222" s="10">
@@ -9316,7 +9306,7 @@
         <v>525</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E223" s="35">
         <v>95</v>
@@ -9328,7 +9318,7 @@
         <v>220</v>
       </c>
       <c r="H223" s="35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I223" s="37"/>
     </row>
@@ -9337,13 +9327,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>774</v>
+        <v>759</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9363,7 +9353,7 @@
       <c r="A225" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="B225" s="28" t="s">
+      <c r="B225" s="27" t="s">
         <v>528</v>
       </c>
       <c r="C225" s="35" t="s">
@@ -9382,19 +9372,19 @@
         <v>215</v>
       </c>
       <c r="H225" s="35">
-        <v>5</v>
-      </c>
-      <c r="I225" s="12"/>
+        <v>4.8</v>
+      </c>
+      <c r="I225" s="11"/>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" s="9" t="s">
         <v>530</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>741</v>
+        <v>238</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>437</v>
@@ -9409,7 +9399,7 @@
         <v>215</v>
       </c>
       <c r="H226" s="35">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I226" s="37"/>
     </row>
@@ -9418,10 +9408,10 @@
         <v>531</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>741</v>
+        <v>238</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>437</v>
@@ -9436,7 +9426,7 @@
         <v>215</v>
       </c>
       <c r="H227" s="35">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I227" s="37"/>
     </row>
@@ -9463,9 +9453,9 @@
         <v>215</v>
       </c>
       <c r="H228" s="35">
-        <v>5</v>
-      </c>
-      <c r="I228" s="12"/>
+        <v>4.8</v>
+      </c>
+      <c r="I228" s="11"/>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="9" t="s">
@@ -9490,9 +9480,9 @@
         <v>215</v>
       </c>
       <c r="H229" s="35">
-        <v>5</v>
-      </c>
-      <c r="I229" s="12"/>
+        <v>4.7</v>
+      </c>
+      <c r="I229" s="11"/>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" s="9" t="s">
@@ -9513,13 +9503,13 @@
       <c r="F230" s="36">
         <v>225</v>
       </c>
-      <c r="G230" s="12">
+      <c r="G230" s="11">
         <v>215</v>
       </c>
       <c r="H230" s="51">
-        <v>5</v>
-      </c>
-      <c r="I230" s="12"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I230" s="11"/>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="9" t="s">
@@ -9532,7 +9522,7 @@
       <c r="F231" s="31"/>
       <c r="G231" s="32"/>
       <c r="H231" s="18"/>
-      <c r="I231" s="12"/>
+      <c r="I231" s="11"/>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="9" t="s">
@@ -9566,7 +9556,7 @@
         <v>215</v>
       </c>
       <c r="H233" s="35">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I233" s="37"/>
     </row>
@@ -9575,13 +9565,13 @@
         <v>544</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9593,10 +9583,10 @@
         <v>215</v>
       </c>
       <c r="H234" s="52">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9604,13 +9594,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>782</v>
+        <v>878</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9619,10 +9609,10 @@
         <v>230</v>
       </c>
       <c r="G235" s="55">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H235" s="51">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I235" s="55" t="s">
         <v>546</v>
@@ -9633,13 +9623,13 @@
         <v>547</v>
       </c>
       <c r="B236" s="51" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="C236" s="51" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="D236" s="51" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="E236" s="51">
         <v>170</v>
@@ -9651,7 +9641,7 @@
         <v>220</v>
       </c>
       <c r="H236" s="51">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I236" s="54" t="s">
         <v>548</v>
@@ -9662,13 +9652,13 @@
         <v>549</v>
       </c>
       <c r="B237" s="51" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="C237" s="51" t="s">
         <v>550</v>
       </c>
       <c r="D237" s="51" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9680,7 +9670,7 @@
         <v>218</v>
       </c>
       <c r="H237" s="51">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I237" s="55" t="s">
         <v>546</v>
@@ -9704,13 +9694,13 @@
         <v>552</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
@@ -9725,7 +9715,7 @@
         <v>5.5</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -9733,13 +9723,13 @@
         <v>553</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -9754,7 +9744,7 @@
         <v>5.7</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -9762,12 +9752,12 @@
         <v>554</v>
       </c>
       <c r="B241" s="51" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="C241" s="51" t="s">
-        <v>796</v>
-      </c>
-      <c r="D241" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>555</v>
       </c>
       <c r="E241" s="51">
@@ -9783,7 +9773,7 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -9791,13 +9781,13 @@
         <v>556</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -9812,7 +9802,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>800</v>
+        <v>548</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -9820,13 +9810,13 @@
         <v>557</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>803</v>
+        <v>879</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -9838,23 +9828,35 @@
         <v>220</v>
       </c>
       <c r="H243" s="35">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="B244" s="38"/>
-      <c r="C244" s="38"/>
-      <c r="D244" s="38"/>
-      <c r="E244" s="38"/>
+      <c r="B244" s="51" t="s">
+        <v>880</v>
+      </c>
+      <c r="C244" s="51" t="s">
+        <v>881</v>
+      </c>
+      <c r="D244" s="51" t="s">
+        <v>879</v>
+      </c>
+      <c r="E244" s="51">
+        <v>150</v>
+      </c>
       <c r="F244" s="38"/>
-      <c r="G244" s="38"/>
-      <c r="H244" s="38"/>
+      <c r="G244" s="55">
+        <v>220</v>
+      </c>
+      <c r="H244" s="35">
+        <v>3.9</v>
+      </c>
       <c r="I244" s="54"/>
     </row>
     <row r="245" spans="1:9">
@@ -9868,20 +9870,20 @@
       <c r="F245" s="38"/>
       <c r="G245" s="38"/>
       <c r="H245" s="38"/>
-      <c r="I245" s="12"/>
+      <c r="I245" s="11"/>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" s="9" t="s">
         <v>560</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>738</v>
+        <v>429</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -9902,7 +9904,7 @@
         <v>561</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>529</v>
@@ -9922,14 +9924,14 @@
       <c r="H247" s="18">
         <v>4.3</v>
       </c>
-      <c r="I247" s="57"/>
+      <c r="I247" s="56"/>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="31" t="s">
         <v>562</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>563</v>
@@ -9949,17 +9951,17 @@
       <c r="H248" s="18">
         <v>5.2</v>
       </c>
-      <c r="I248" s="58"/>
+      <c r="I248" s="57"/>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="31" t="s">
         <v>564</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>810</v>
+        <v>439</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>429</v>
@@ -9967,7 +9969,7 @@
       <c r="E249" s="32">
         <v>105</v>
       </c>
-      <c r="F249" s="56">
+      <c r="F249" s="58">
         <v>150</v>
       </c>
       <c r="G249" s="32">
@@ -9976,14 +9978,14 @@
       <c r="H249" s="32">
         <v>3.4</v>
       </c>
-      <c r="I249" s="58"/>
+      <c r="I249" s="57"/>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="31" t="s">
         <v>565</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>153</v>
@@ -9994,11 +9996,11 @@
       <c r="E250" s="32">
         <v>108</v>
       </c>
-      <c r="F250" s="56">
+      <c r="F250" s="58">
         <v>150</v>
       </c>
       <c r="G250" s="32">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H250" s="32">
         <v>3.4</v>
@@ -10010,7 +10012,7 @@
         <v>566</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>567</v>
@@ -10021,14 +10023,14 @@
       <c r="E251" s="18">
         <v>116</v>
       </c>
-      <c r="F251" s="56">
+      <c r="F251" s="58">
         <v>180</v>
       </c>
       <c r="G251" s="32">
         <v>215</v>
       </c>
       <c r="H251" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I251" s="32"/>
     </row>
@@ -10037,10 +10039,10 @@
         <v>568</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>810</v>
+        <v>439</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>429</v>
@@ -10048,7 +10050,7 @@
       <c r="E252" s="18">
         <v>105</v>
       </c>
-      <c r="F252" s="56">
+      <c r="F252" s="58">
         <v>155</v>
       </c>
       <c r="G252" s="32">
@@ -10064,7 +10066,7 @@
         <v>569</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>567</v>
@@ -10075,14 +10077,14 @@
       <c r="E253" s="18">
         <v>116</v>
       </c>
-      <c r="F253" s="56">
+      <c r="F253" s="58">
         <v>180</v>
       </c>
       <c r="G253" s="32">
         <v>215</v>
       </c>
       <c r="H253" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I253" s="32"/>
     </row>
@@ -10091,19 +10093,19 @@
         <v>570</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
       </c>
       <c r="F254" s="31">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G254" s="32">
         <v>215</v>
@@ -10112,7 +10114,7 @@
         <v>5.5</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10120,7 +10122,7 @@
         <v>571</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>572</v>
@@ -10134,11 +10136,11 @@
       <c r="F255" s="31">
         <v>130</v>
       </c>
-      <c r="G255" s="57">
+      <c r="G255" s="56">
         <v>208</v>
       </c>
       <c r="H255" s="59">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I255" s="54"/>
     </row>
@@ -10147,19 +10149,19 @@
         <v>573</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>819</v>
+        <v>333</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="E256" s="52">
         <v>185</v>
       </c>
       <c r="F256" s="36">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G256" s="53">
         <v>215</v>
@@ -10168,7 +10170,7 @@
         <v>5.3</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>800</v>
+        <v>548</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10176,13 +10178,13 @@
         <v>574</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>822</v>
+        <v>321</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>738</v>
+        <v>429</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10194,7 +10196,7 @@
         <v>215</v>
       </c>
       <c r="H257" s="60">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I257" s="60"/>
     </row>
@@ -10202,13 +10204,27 @@
       <c r="A258" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="B258" s="36"/>
-      <c r="C258" s="36"/>
-      <c r="D258" s="36"/>
-      <c r="E258" s="36"/>
-      <c r="F258" s="36"/>
-      <c r="G258" s="36"/>
-      <c r="H258" s="60"/>
+      <c r="B258" s="18" t="s">
+        <v>792</v>
+      </c>
+      <c r="C258" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D258" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="E258" s="32">
+        <v>108</v>
+      </c>
+      <c r="F258" s="58">
+        <v>160</v>
+      </c>
+      <c r="G258" s="32">
+        <v>215</v>
+      </c>
+      <c r="H258" s="32">
+        <v>3.6</v>
+      </c>
       <c r="I258" s="60"/>
     </row>
     <row r="259" spans="1:9">
@@ -10248,15 +10264,15 @@
         <v>580</v>
       </c>
       <c r="D261" s="49" t="s">
-        <v>823</v>
+        <v>802</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
       </c>
-      <c r="F261" s="27">
+      <c r="F261" s="29">
         <v>167</v>
       </c>
-      <c r="G261" s="12">
+      <c r="G261" s="11">
         <v>210</v>
       </c>
       <c r="H261" s="10">
@@ -10269,7 +10285,7 @@
         <v>581</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>582</v>
@@ -10280,14 +10296,14 @@
       <c r="E262" s="10">
         <v>87</v>
       </c>
-      <c r="F262" s="27">
+      <c r="F262" s="29">
         <v>125</v>
       </c>
-      <c r="G262" s="12">
+      <c r="G262" s="11">
         <v>208</v>
       </c>
       <c r="H262" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I262" s="60"/>
     </row>
@@ -10295,16 +10311,16 @@
       <c r="A263" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="B263" s="28" t="s">
+      <c r="B263" s="27" t="s">
         <v>585</v>
       </c>
-      <c r="C263" s="28" t="s">
+      <c r="C263" s="27" t="s">
         <v>586</v>
       </c>
-      <c r="D263" s="28" t="s">
+      <c r="D263" s="27" t="s">
         <v>587</v>
       </c>
-      <c r="E263" s="28">
+      <c r="E263" s="27">
         <v>115</v>
       </c>
       <c r="F263" s="36">
@@ -10313,8 +10329,8 @@
       <c r="G263" s="37">
         <v>208</v>
       </c>
-      <c r="H263" s="28">
-        <v>3.4</v>
+      <c r="H263" s="27">
+        <v>3.3</v>
       </c>
       <c r="I263" s="60"/>
     </row>
@@ -10337,7 +10353,7 @@
       <c r="F264" s="36">
         <v>105</v>
       </c>
-      <c r="G264" s="12">
+      <c r="G264" s="11">
         <v>208</v>
       </c>
       <c r="H264" s="10">
@@ -10377,13 +10393,13 @@
         <v>596</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>825</v>
+        <v>804</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10395,7 +10411,7 @@
         <v>215</v>
       </c>
       <c r="H266" s="35">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I266" s="60"/>
     </row>
@@ -10404,13 +10420,13 @@
         <v>597</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>830</v>
+        <v>144</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10418,7 +10434,7 @@
       <c r="F267" s="9">
         <v>98</v>
       </c>
-      <c r="G267" s="12">
+      <c r="G267" s="11">
         <v>220</v>
       </c>
       <c r="H267" s="10">
@@ -10574,16 +10590,16 @@
       <c r="A278" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="B278" s="28" t="s">
-        <v>831</v>
-      </c>
-      <c r="C278" s="28" t="s">
-        <v>832</v>
-      </c>
-      <c r="D278" s="28" t="s">
-        <v>833</v>
-      </c>
-      <c r="E278" s="28">
+      <c r="B278" s="27" t="s">
+        <v>809</v>
+      </c>
+      <c r="C278" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="D278" s="27" t="s">
+        <v>810</v>
+      </c>
+      <c r="E278" s="27">
         <v>159</v>
       </c>
       <c r="F278" s="62">
@@ -10592,8 +10608,8 @@
       <c r="G278" s="20">
         <v>212</v>
       </c>
-      <c r="H278" s="28">
-        <v>5</v>
+      <c r="H278" s="27">
+        <v>4.9000000000000004</v>
       </c>
       <c r="I278" s="60"/>
     </row>
@@ -10602,10 +10618,10 @@
         <v>612</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>834</v>
+        <v>811</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>835</v>
+        <v>812</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>144</v>
@@ -10616,7 +10632,7 @@
       <c r="F279" s="9">
         <v>80</v>
       </c>
-      <c r="G279" s="12">
+      <c r="G279" s="11">
         <v>220</v>
       </c>
       <c r="H279" s="10">
@@ -10629,19 +10645,19 @@
         <v>613</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>836</v>
+        <v>813</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>838</v>
+        <v>489</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
         <v>68</v>
       </c>
-      <c r="G280" s="12">
+      <c r="G280" s="11">
         <v>210</v>
       </c>
       <c r="H280" s="10">
@@ -10668,7 +10684,7 @@
       <c r="F281" s="9">
         <v>95</v>
       </c>
-      <c r="G281" s="12">
+      <c r="G281" s="11">
         <v>222</v>
       </c>
       <c r="H281" s="10">
@@ -10681,7 +10697,7 @@
         <v>617</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>839</v>
+        <v>815</v>
       </c>
       <c r="C282" s="49" t="s">
         <v>618</v>
@@ -10695,11 +10711,11 @@
       <c r="F282" s="9">
         <v>110</v>
       </c>
-      <c r="G282" s="12">
+      <c r="G282" s="11">
         <v>215</v>
       </c>
       <c r="H282" s="10">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I282" s="60"/>
     </row>
@@ -10708,10 +10724,10 @@
         <v>619</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>840</v>
+        <v>816</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>841</v>
+        <v>817</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -10722,7 +10738,7 @@
       <c r="F283" s="9">
         <v>140</v>
       </c>
-      <c r="G283" s="12">
+      <c r="G283" s="11">
         <v>208</v>
       </c>
       <c r="H283" s="10">
@@ -10734,14 +10750,14 @@
       <c r="A284" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="B284" s="28" t="s">
-        <v>842</v>
+      <c r="B284" s="27" t="s">
+        <v>818</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>843</v>
+        <v>819</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -10753,7 +10769,7 @@
         <v>208</v>
       </c>
       <c r="H284" s="60">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I284" s="60"/>
     </row>
@@ -10768,7 +10784,7 @@
         <v>623</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -10776,11 +10792,11 @@
       <c r="F285" s="36">
         <v>108</v>
       </c>
-      <c r="G285" s="12">
+      <c r="G285" s="11">
         <v>208</v>
       </c>
       <c r="H285" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I285" s="60"/>
     </row>
@@ -10789,10 +10805,10 @@
         <v>624</v>
       </c>
       <c r="B286" s="52" t="s">
-        <v>845</v>
+        <v>821</v>
       </c>
       <c r="C286" s="52" t="s">
-        <v>846</v>
+        <v>822</v>
       </c>
       <c r="D286" s="52" t="s">
         <v>625</v>
@@ -10816,13 +10832,13 @@
         <v>626</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>847</v>
+        <v>823</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>848</v>
+        <v>824</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -10834,7 +10850,7 @@
         <v>218</v>
       </c>
       <c r="H287" s="52">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I287" s="61"/>
     </row>
@@ -10842,25 +10858,25 @@
       <c r="A288" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="B288" s="28" t="s">
-        <v>850</v>
-      </c>
-      <c r="C288" s="28" t="s">
+      <c r="B288" s="27" t="s">
+        <v>826</v>
+      </c>
+      <c r="C288" s="27" t="s">
         <v>628</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="E288" s="28">
+        <v>4</v>
+      </c>
+      <c r="E288" s="27">
         <v>95</v>
       </c>
       <c r="F288" s="9">
         <v>130</v>
       </c>
-      <c r="G288" s="12">
+      <c r="G288" s="11">
         <v>208</v>
       </c>
-      <c r="H288" s="28">
+      <c r="H288" s="27">
         <v>5</v>
       </c>
       <c r="I288" s="61"/>
@@ -10884,14 +10900,14 @@
       <c r="F289" s="36">
         <v>186</v>
       </c>
-      <c r="G289" s="12">
+      <c r="G289" s="11">
         <v>215</v>
       </c>
       <c r="H289" s="10">
         <v>3.9</v>
       </c>
-      <c r="I289" s="12" t="s">
-        <v>851</v>
+      <c r="I289" s="11" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -10917,7 +10933,7 @@
         <v>220</v>
       </c>
       <c r="H290" s="24">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I290" s="61"/>
     </row>
@@ -10926,7 +10942,7 @@
         <v>636</v>
       </c>
       <c r="B291" s="64" t="s">
-        <v>852</v>
+        <v>828</v>
       </c>
       <c r="C291" s="64" t="s">
         <v>637</v>
@@ -10944,7 +10960,7 @@
         <v>220</v>
       </c>
       <c r="H291" s="64">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I291" s="61"/>
     </row>
@@ -10953,7 +10969,7 @@
         <v>639</v>
       </c>
       <c r="B292" s="64" t="s">
-        <v>853</v>
+        <v>829</v>
       </c>
       <c r="C292" s="64" t="s">
         <v>640</v>
@@ -10980,10 +10996,10 @@
         <v>642</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>854</v>
+        <v>830</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>855</v>
+        <v>831</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11007,13 +11023,13 @@
         <v>643</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>856</v>
+        <v>832</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>737</v>
+        <v>445</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11034,7 +11050,7 @@
         <v>644</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>858</v>
+        <v>834</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>645</v>
@@ -11044,7 +11060,7 @@
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="9"/>
-      <c r="G295" s="12">
+      <c r="G295" s="11">
         <v>215</v>
       </c>
       <c r="H295" s="10">
@@ -11069,7 +11085,7 @@
       <c r="F296" s="36">
         <v>120</v>
       </c>
-      <c r="G296" s="12">
+      <c r="G296" s="11">
         <v>208</v>
       </c>
       <c r="H296" s="35">
@@ -11082,13 +11098,13 @@
         <v>651</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>859</v>
+        <v>835</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>860</v>
+        <v>836</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>861</v>
+        <v>837</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11100,7 +11116,7 @@
         <v>215</v>
       </c>
       <c r="H297" s="18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I297" s="54"/>
     </row>
@@ -11122,13 +11138,13 @@
         <v>653</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>862</v>
+        <v>838</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>863</v>
+        <v>839</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>864</v>
+        <v>840</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11140,10 +11156,10 @@
         <v>218</v>
       </c>
       <c r="H299" s="51">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>865</v>
+        <v>841</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11176,49 +11192,49 @@
       <c r="A302" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B302" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="C302" s="12" t="s">
-        <v>658</v>
-      </c>
-      <c r="D302" s="12" t="s">
+      <c r="B302" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="C302" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="D302" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="E302" s="12">
+      <c r="E302" s="11">
         <v>150</v>
       </c>
-      <c r="F302" s="13">
+      <c r="F302" s="12">
         <v>200</v>
       </c>
-      <c r="G302" s="12">
+      <c r="G302" s="11">
         <v>215</v>
       </c>
-      <c r="H302" s="12">
+      <c r="H302" s="11">
         <v>4.5999999999999996</v>
       </c>
       <c r="I302" s="61"/>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B303" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="C303" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="D303" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>661</v>
-      </c>
-      <c r="D303" s="10" t="s">
-        <v>662</v>
-      </c>
-      <c r="E303" s="12">
+      <c r="E303" s="11">
         <v>140</v>
       </c>
-      <c r="F303" s="13">
+      <c r="F303" s="12">
         <v>180</v>
       </c>
-      <c r="G303" s="12">
+      <c r="G303" s="11">
         <v>215</v>
       </c>
       <c r="H303" s="10">
@@ -11228,16 +11244,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" s="64" t="s">
+        <v>662</v>
+      </c>
+      <c r="C304" s="64" t="s">
+        <v>251</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>663</v>
-      </c>
-      <c r="B304" s="64" t="s">
-        <v>664</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>866</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>665</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11249,24 +11265,24 @@
         <v>218</v>
       </c>
       <c r="H304" s="64">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>867</v>
+        <v>842</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="9" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>868</v>
+        <v>843</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>869</v>
+        <v>844</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>870</v>
+        <v>845</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11278,13 +11294,13 @@
         <v>225</v>
       </c>
       <c r="H305" s="61">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I305" s="61"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B306" s="36"/>
       <c r="C306" s="36"/>
@@ -11297,7 +11313,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B307" s="36"/>
       <c r="C307" s="36"/>
@@ -11310,7 +11326,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B308" s="36"/>
       <c r="C308" s="36"/>
@@ -11323,7 +11339,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B309" s="36"/>
       <c r="C309" s="36"/>
@@ -11336,7 +11352,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B310" s="36"/>
       <c r="C310" s="36"/>
@@ -11349,16 +11365,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B311" s="35" t="s">
+        <v>671</v>
+      </c>
+      <c r="C311" s="35" t="s">
+        <v>675</v>
+      </c>
+      <c r="D311" s="35" t="s">
         <v>672</v>
-      </c>
-      <c r="B311" s="35" t="s">
-        <v>673</v>
-      </c>
-      <c r="C311" s="35" t="s">
-        <v>871</v>
-      </c>
-      <c r="D311" s="35" t="s">
-        <v>675</v>
       </c>
       <c r="E311" s="35">
         <v>85</v>
@@ -11376,16 +11392,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B312" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D312" s="10" t="s">
         <v>676</v>
-      </c>
-      <c r="B312" s="10" t="s">
-        <v>677</v>
-      </c>
-      <c r="C312" s="10" t="s">
-        <v>674</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>678</v>
       </c>
       <c r="E312" s="10">
         <v>73</v>
@@ -11393,7 +11409,7 @@
       <c r="F312" s="9">
         <v>98</v>
       </c>
-      <c r="G312" s="12">
+      <c r="G312" s="11">
         <v>208</v>
       </c>
       <c r="H312" s="10">
@@ -11403,7 +11419,7 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B313" s="36"/>
       <c r="C313" s="36"/>
@@ -11416,7 +11432,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B314" s="36"/>
       <c r="C314" s="36"/>
@@ -11429,16 +11445,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>872</v>
+        <v>846</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>873</v>
-      </c>
-      <c r="D315" s="12" t="s">
-        <v>874</v>
+        <v>847</v>
+      </c>
+      <c r="D315" s="11" t="s">
+        <v>848</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11450,24 +11466,24 @@
         <v>225</v>
       </c>
       <c r="H315" s="61">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>875</v>
+        <v>849</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="9" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>877</v>
-      </c>
-      <c r="D316" s="12" t="s">
-        <v>878</v>
+        <v>851</v>
+      </c>
+      <c r="D316" s="11" t="s">
+        <v>852</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11482,77 +11498,77 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="B317" s="12" t="s">
-        <v>880</v>
-      </c>
-      <c r="C317" s="12" t="s">
-        <v>881</v>
-      </c>
-      <c r="D317" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="E317" s="12">
+        <v>681</v>
+      </c>
+      <c r="B317" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="C317" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="D317" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="E317" s="11">
         <v>110</v>
       </c>
-      <c r="F317" s="13">
+      <c r="F317" s="12">
         <v>160</v>
       </c>
-      <c r="G317" s="12">
+      <c r="G317" s="11">
         <v>188</v>
       </c>
-      <c r="H317" s="12">
+      <c r="H317" s="11">
         <v>3.7</v>
       </c>
-      <c r="I317" s="12" t="s">
-        <v>883</v>
+      <c r="I317" s="11" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="B318" s="12" t="s">
-        <v>880</v>
-      </c>
-      <c r="C318" s="12" t="s">
-        <v>884</v>
-      </c>
-      <c r="D318" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="E318" s="12">
+        <v>682</v>
+      </c>
+      <c r="B318" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="C318" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="D318" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="E318" s="11">
         <v>110</v>
       </c>
-      <c r="F318" s="13">
+      <c r="F318" s="12">
         <v>160</v>
       </c>
-      <c r="G318" s="12">
+      <c r="G318" s="11">
         <v>208</v>
       </c>
-      <c r="H318" s="12">
-        <v>4</v>
-      </c>
-      <c r="I318" s="12"/>
+      <c r="H318" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="I318" s="11"/>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="9" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>885</v>
+        <v>858</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>886</v>
+        <v>859</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>887</v>
+        <v>860</v>
       </c>
       <c r="E319" s="18">
         <v>205</v>
@@ -11566,28 +11582,28 @@
       <c r="H319" s="18">
         <v>5.5</v>
       </c>
-      <c r="I319" s="12" t="s">
-        <v>888</v>
+      <c r="I319" s="11" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="9" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>889</v>
+        <v>862</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>790</v>
+        <v>885</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>890</v>
+        <v>863</v>
       </c>
       <c r="E320" s="18">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F320" s="31">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G320" s="32">
         <v>218</v>
@@ -11595,22 +11611,22 @@
       <c r="H320" s="18">
         <v>6</v>
       </c>
-      <c r="I320" s="12" t="s">
-        <v>891</v>
+      <c r="I320" s="11" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="9" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>892</v>
+        <v>864</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>893</v>
+        <v>865</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>894</v>
+        <v>866</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11624,22 +11640,22 @@
       <c r="H321" s="18">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I321" s="12" t="s">
-        <v>895</v>
+      <c r="I321" s="11" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="9" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>896</v>
+        <v>868</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>897</v>
+        <v>869</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>887</v>
+        <v>860</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11653,22 +11669,22 @@
       <c r="H322" s="18">
         <v>6</v>
       </c>
-      <c r="I322" s="12" t="s">
-        <v>898</v>
+      <c r="I322" s="11" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>899</v>
+        <v>871</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>900</v>
+        <v>88</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>894</v>
+        <v>866</v>
       </c>
       <c r="E323" s="18">
         <v>155</v>
@@ -11680,24 +11696,24 @@
         <v>215</v>
       </c>
       <c r="H323" s="18">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I323" s="12" t="s">
-        <v>901</v>
+        <v>4.8</v>
+      </c>
+      <c r="I323" s="11" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="9" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>902</v>
+        <v>873</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>903</v>
+        <v>874</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>887</v>
+        <v>860</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -11711,13 +11727,13 @@
       <c r="H324" s="18">
         <v>6.2</v>
       </c>
-      <c r="I324" s="12" t="s">
-        <v>898</v>
+      <c r="I324" s="11" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B325" s="36"/>
       <c r="C325" s="36"/>
@@ -11728,28 +11744,1021 @@
       <c r="H325" s="61"/>
       <c r="I325" s="61"/>
     </row>
+    <row r="326" spans="1:9">
+      <c r="A326" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="B326" s="36"/>
+      <c r="C326" s="36"/>
+      <c r="D326" s="36"/>
+      <c r="E326" s="36"/>
+      <c r="F326" s="36"/>
+      <c r="G326" s="36"/>
+      <c r="H326" s="61"/>
+      <c r="I326" s="61"/>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="B327" s="36"/>
+      <c r="C327" s="36"/>
+      <c r="D327" s="36"/>
+      <c r="E327" s="36"/>
+      <c r="F327" s="36"/>
+      <c r="G327" s="36"/>
+      <c r="H327" s="61"/>
+      <c r="I327" s="61"/>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="B328" s="36"/>
+      <c r="C328" s="36"/>
+      <c r="D328" s="36"/>
+      <c r="E328" s="36"/>
+      <c r="F328" s="36"/>
+      <c r="G328" s="36"/>
+      <c r="H328" s="61"/>
+      <c r="I328" s="61"/>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="B329" s="36"/>
+      <c r="C329" s="36"/>
+      <c r="D329" s="36"/>
+      <c r="E329" s="36"/>
+      <c r="F329" s="36"/>
+      <c r="G329" s="36"/>
+      <c r="H329" s="61"/>
+      <c r="I329" s="61"/>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="B330" s="36"/>
+      <c r="C330" s="36"/>
+      <c r="D330" s="36"/>
+      <c r="E330" s="36"/>
+      <c r="F330" s="36"/>
+      <c r="G330" s="36"/>
+      <c r="H330" s="61"/>
+      <c r="I330" s="61"/>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="B331" s="36"/>
+      <c r="C331" s="36"/>
+      <c r="D331" s="36"/>
+      <c r="E331" s="36"/>
+      <c r="F331" s="36"/>
+      <c r="G331" s="36"/>
+      <c r="H331" s="61"/>
+      <c r="I331" s="61"/>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="B332" s="36"/>
+      <c r="C332" s="36"/>
+      <c r="D332" s="36"/>
+      <c r="E332" s="36"/>
+      <c r="F332" s="36"/>
+      <c r="G332" s="36"/>
+      <c r="H332" s="61"/>
+      <c r="I332" s="61"/>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="B333" s="36"/>
+      <c r="C333" s="36"/>
+      <c r="D333" s="36"/>
+      <c r="E333" s="36"/>
+      <c r="F333" s="36"/>
+      <c r="G333" s="36"/>
+      <c r="H333" s="61"/>
+      <c r="I333" s="61"/>
+    </row>
+    <row r="334" spans="1:9">
+      <c r="A334" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="B334" s="36"/>
+      <c r="C334" s="36"/>
+      <c r="D334" s="36"/>
+      <c r="E334" s="36"/>
+      <c r="F334" s="36"/>
+      <c r="G334" s="36"/>
+      <c r="H334" s="61"/>
+      <c r="I334" s="61"/>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="B335" s="36"/>
+      <c r="C335" s="36"/>
+      <c r="D335" s="36"/>
+      <c r="E335" s="36"/>
+      <c r="F335" s="36"/>
+      <c r="G335" s="36"/>
+      <c r="H335" s="61"/>
+      <c r="I335" s="61"/>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B336" s="36"/>
+      <c r="C336" s="36"/>
+      <c r="D336" s="36"/>
+      <c r="E336" s="36"/>
+      <c r="F336" s="36"/>
+      <c r="G336" s="36"/>
+      <c r="H336" s="61"/>
+      <c r="I336" s="61"/>
+    </row>
+    <row r="337" spans="1:9">
+      <c r="A337" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="B337" s="36"/>
+      <c r="C337" s="36"/>
+      <c r="D337" s="36"/>
+      <c r="E337" s="36"/>
+      <c r="F337" s="36"/>
+      <c r="G337" s="36"/>
+      <c r="H337" s="61"/>
+      <c r="I337" s="61"/>
+    </row>
+    <row r="338" spans="1:9">
+      <c r="A338" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="B338" s="36"/>
+      <c r="C338" s="36"/>
+      <c r="D338" s="36"/>
+      <c r="E338" s="36"/>
+      <c r="F338" s="36"/>
+      <c r="G338" s="36"/>
+      <c r="H338" s="61"/>
+      <c r="I338" s="61"/>
+    </row>
+    <row r="339" spans="1:9">
+      <c r="A339" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="B339" s="36"/>
+      <c r="C339" s="36"/>
+      <c r="D339" s="36"/>
+      <c r="E339" s="36"/>
+      <c r="F339" s="36"/>
+      <c r="G339" s="36"/>
+      <c r="H339" s="61"/>
+      <c r="I339" s="61"/>
+    </row>
+    <row r="340" spans="1:9">
+      <c r="A340" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="B340" s="36"/>
+      <c r="C340" s="36"/>
+      <c r="D340" s="36"/>
+      <c r="E340" s="36"/>
+      <c r="F340" s="36"/>
+      <c r="G340" s="36"/>
+      <c r="H340" s="61"/>
+      <c r="I340" s="61"/>
+    </row>
+    <row r="341" spans="1:9">
+      <c r="A341" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="B341" s="36"/>
+      <c r="C341" s="36"/>
+      <c r="D341" s="36"/>
+      <c r="E341" s="36"/>
+      <c r="F341" s="36"/>
+      <c r="G341" s="36"/>
+      <c r="H341" s="61"/>
+      <c r="I341" s="61"/>
+    </row>
+    <row r="342" spans="1:9">
+      <c r="A342" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="B342" s="36"/>
+      <c r="C342" s="36"/>
+      <c r="D342" s="36"/>
+      <c r="E342" s="36"/>
+      <c r="F342" s="36"/>
+      <c r="G342" s="36"/>
+      <c r="H342" s="61"/>
+      <c r="I342" s="61"/>
+    </row>
+    <row r="343" spans="1:9">
+      <c r="A343" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="B343" s="36"/>
+      <c r="C343" s="36"/>
+      <c r="D343" s="36"/>
+      <c r="E343" s="36"/>
+      <c r="F343" s="36"/>
+      <c r="G343" s="36"/>
+      <c r="H343" s="61"/>
+      <c r="I343" s="61"/>
+    </row>
+    <row r="344" spans="1:9">
+      <c r="A344" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="B344" s="36"/>
+      <c r="C344" s="36"/>
+      <c r="D344" s="36"/>
+      <c r="E344" s="36"/>
+      <c r="F344" s="36"/>
+      <c r="G344" s="36"/>
+      <c r="H344" s="61"/>
+      <c r="I344" s="61"/>
+    </row>
+    <row r="345" spans="1:9">
+      <c r="A345" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="B345" s="36"/>
+      <c r="C345" s="36"/>
+      <c r="D345" s="36"/>
+      <c r="E345" s="36"/>
+      <c r="F345" s="36"/>
+      <c r="G345" s="36"/>
+      <c r="H345" s="61"/>
+      <c r="I345" s="61"/>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="B346" s="36"/>
+      <c r="C346" s="36"/>
+      <c r="D346" s="36"/>
+      <c r="E346" s="36"/>
+      <c r="F346" s="36"/>
+      <c r="G346" s="36"/>
+      <c r="H346" s="61"/>
+      <c r="I346" s="61"/>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="B347" s="36"/>
+      <c r="C347" s="36"/>
+      <c r="D347" s="36"/>
+      <c r="E347" s="36"/>
+      <c r="F347" s="36"/>
+      <c r="G347" s="36"/>
+      <c r="H347" s="61"/>
+      <c r="I347" s="61"/>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="B348" s="36"/>
+      <c r="C348" s="36"/>
+      <c r="D348" s="36"/>
+      <c r="E348" s="36"/>
+      <c r="F348" s="36"/>
+      <c r="G348" s="36"/>
+      <c r="H348" s="61"/>
+      <c r="I348" s="61"/>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="B349" s="36"/>
+      <c r="C349" s="36"/>
+      <c r="D349" s="36"/>
+      <c r="E349" s="36"/>
+      <c r="F349" s="36"/>
+      <c r="G349" s="36"/>
+      <c r="H349" s="61"/>
+      <c r="I349" s="61"/>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="B350" s="36"/>
+      <c r="C350" s="36"/>
+      <c r="D350" s="36"/>
+      <c r="E350" s="36"/>
+      <c r="F350" s="36"/>
+      <c r="G350" s="36"/>
+      <c r="H350" s="61"/>
+      <c r="I350" s="61"/>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="B351" s="36"/>
+      <c r="C351" s="36"/>
+      <c r="D351" s="36"/>
+      <c r="E351" s="36"/>
+      <c r="F351" s="36"/>
+      <c r="G351" s="36"/>
+      <c r="H351" s="61"/>
+      <c r="I351" s="61"/>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="B352" s="36"/>
+      <c r="C352" s="36"/>
+      <c r="D352" s="36"/>
+      <c r="E352" s="36"/>
+      <c r="F352" s="36"/>
+      <c r="G352" s="36"/>
+      <c r="H352" s="61"/>
+      <c r="I352" s="61"/>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="B353" s="36"/>
+      <c r="C353" s="36"/>
+      <c r="D353" s="36"/>
+      <c r="E353" s="36"/>
+      <c r="F353" s="36"/>
+      <c r="G353" s="36"/>
+      <c r="H353" s="61"/>
+      <c r="I353" s="61"/>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="B354" s="36"/>
+      <c r="C354" s="36"/>
+      <c r="D354" s="36"/>
+      <c r="E354" s="36"/>
+      <c r="F354" s="36"/>
+      <c r="G354" s="36"/>
+      <c r="H354" s="61"/>
+      <c r="I354" s="61"/>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="B355" s="36"/>
+      <c r="C355" s="36"/>
+      <c r="D355" s="36"/>
+      <c r="E355" s="36"/>
+      <c r="F355" s="36"/>
+      <c r="G355" s="36"/>
+      <c r="H355" s="61"/>
+      <c r="I355" s="61"/>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="B356" s="36"/>
+      <c r="C356" s="36"/>
+      <c r="D356" s="36"/>
+      <c r="E356" s="36"/>
+      <c r="F356" s="36"/>
+      <c r="G356" s="36"/>
+      <c r="H356" s="61"/>
+      <c r="I356" s="61"/>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="B357" s="36"/>
+      <c r="C357" s="36"/>
+      <c r="D357" s="36"/>
+      <c r="E357" s="36"/>
+      <c r="F357" s="36"/>
+      <c r="G357" s="36"/>
+      <c r="H357" s="61"/>
+      <c r="I357" s="61"/>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="B358" s="36"/>
+      <c r="C358" s="36"/>
+      <c r="D358" s="36"/>
+      <c r="E358" s="36"/>
+      <c r="F358" s="36"/>
+      <c r="G358" s="36"/>
+      <c r="H358" s="61"/>
+      <c r="I358" s="61"/>
+    </row>
+    <row r="359" spans="1:9">
+      <c r="A359" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="B359" s="36"/>
+      <c r="C359" s="36"/>
+      <c r="D359" s="36"/>
+      <c r="E359" s="36"/>
+      <c r="F359" s="36"/>
+      <c r="G359" s="36"/>
+      <c r="H359" s="61"/>
+      <c r="I359" s="61"/>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="B360" s="36"/>
+      <c r="C360" s="36"/>
+      <c r="D360" s="36"/>
+      <c r="E360" s="36"/>
+      <c r="F360" s="36"/>
+      <c r="G360" s="36"/>
+      <c r="H360" s="61"/>
+      <c r="I360" s="61"/>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B361" s="36"/>
+      <c r="C361" s="36"/>
+      <c r="D361" s="36"/>
+      <c r="E361" s="36"/>
+      <c r="F361" s="36"/>
+      <c r="G361" s="36"/>
+      <c r="H361" s="61"/>
+      <c r="I361" s="61"/>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="B362" s="36"/>
+      <c r="C362" s="36"/>
+      <c r="D362" s="36"/>
+      <c r="E362" s="36"/>
+      <c r="F362" s="36"/>
+      <c r="G362" s="36"/>
+      <c r="H362" s="61"/>
+      <c r="I362" s="61"/>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B363" s="36"/>
+      <c r="C363" s="36"/>
+      <c r="D363" s="36"/>
+      <c r="E363" s="36"/>
+      <c r="F363" s="36"/>
+      <c r="G363" s="36"/>
+      <c r="H363" s="61"/>
+      <c r="I363" s="61"/>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="B364" s="36"/>
+      <c r="C364" s="36"/>
+      <c r="D364" s="36"/>
+      <c r="E364" s="36"/>
+      <c r="F364" s="36"/>
+      <c r="G364" s="36"/>
+      <c r="H364" s="61"/>
+      <c r="I364" s="61"/>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="B365" s="36"/>
+      <c r="C365" s="36"/>
+      <c r="D365" s="36"/>
+      <c r="E365" s="36"/>
+      <c r="F365" s="36"/>
+      <c r="G365" s="36"/>
+      <c r="H365" s="61"/>
+      <c r="I365" s="61"/>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="B366" s="36"/>
+      <c r="C366" s="36"/>
+      <c r="D366" s="36"/>
+      <c r="E366" s="36"/>
+      <c r="F366" s="36"/>
+      <c r="G366" s="36"/>
+      <c r="H366" s="61"/>
+      <c r="I366" s="61"/>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="B367" s="36"/>
+      <c r="C367" s="36"/>
+      <c r="D367" s="36"/>
+      <c r="E367" s="36"/>
+      <c r="F367" s="36"/>
+      <c r="G367" s="36"/>
+      <c r="H367" s="61"/>
+      <c r="I367" s="61"/>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368" s="9" t="s">
+        <v>929</v>
+      </c>
+      <c r="B368" s="36"/>
+      <c r="C368" s="36"/>
+      <c r="D368" s="36"/>
+      <c r="E368" s="36"/>
+      <c r="F368" s="36"/>
+      <c r="G368" s="36"/>
+      <c r="H368" s="61"/>
+      <c r="I368" s="61"/>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369" s="9" t="s">
+        <v>930</v>
+      </c>
+      <c r="B369" s="36"/>
+      <c r="C369" s="36"/>
+      <c r="D369" s="36"/>
+      <c r="E369" s="36"/>
+      <c r="F369" s="36"/>
+      <c r="G369" s="36"/>
+      <c r="H369" s="61"/>
+      <c r="I369" s="61"/>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="B370" s="36"/>
+      <c r="C370" s="36"/>
+      <c r="D370" s="36"/>
+      <c r="E370" s="36"/>
+      <c r="F370" s="36"/>
+      <c r="G370" s="36"/>
+      <c r="H370" s="61"/>
+      <c r="I370" s="61"/>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="B371" s="36"/>
+      <c r="C371" s="36"/>
+      <c r="D371" s="36"/>
+      <c r="E371" s="36"/>
+      <c r="F371" s="36"/>
+      <c r="G371" s="36"/>
+      <c r="H371" s="61"/>
+      <c r="I371" s="61"/>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="B372" s="36"/>
+      <c r="C372" s="36"/>
+      <c r="D372" s="36"/>
+      <c r="E372" s="36"/>
+      <c r="F372" s="36"/>
+      <c r="G372" s="36"/>
+      <c r="H372" s="61"/>
+      <c r="I372" s="61"/>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="B373" s="36"/>
+      <c r="C373" s="36"/>
+      <c r="D373" s="36"/>
+      <c r="E373" s="36"/>
+      <c r="F373" s="36"/>
+      <c r="G373" s="36"/>
+      <c r="H373" s="61"/>
+      <c r="I373" s="61"/>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="B374" s="36"/>
+      <c r="C374" s="36"/>
+      <c r="D374" s="36"/>
+      <c r="E374" s="36"/>
+      <c r="F374" s="36"/>
+      <c r="G374" s="36"/>
+      <c r="H374" s="61"/>
+      <c r="I374" s="61"/>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375" s="9" t="s">
+        <v>936</v>
+      </c>
+      <c r="B375" s="36"/>
+      <c r="C375" s="36"/>
+      <c r="D375" s="36"/>
+      <c r="E375" s="36"/>
+      <c r="F375" s="36"/>
+      <c r="G375" s="36"/>
+      <c r="H375" s="61"/>
+      <c r="I375" s="61"/>
+    </row>
+    <row r="376" spans="1:9">
+      <c r="A376" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="B376" s="36"/>
+      <c r="C376" s="36"/>
+      <c r="D376" s="36"/>
+      <c r="E376" s="36"/>
+      <c r="F376" s="36"/>
+      <c r="G376" s="36"/>
+      <c r="H376" s="61"/>
+      <c r="I376" s="61"/>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="B377" s="36"/>
+      <c r="C377" s="36"/>
+      <c r="D377" s="36"/>
+      <c r="E377" s="36"/>
+      <c r="F377" s="36"/>
+      <c r="G377" s="36"/>
+      <c r="H377" s="61"/>
+      <c r="I377" s="61"/>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="B378" s="36"/>
+      <c r="C378" s="36"/>
+      <c r="D378" s="36"/>
+      <c r="E378" s="36"/>
+      <c r="F378" s="36"/>
+      <c r="G378" s="36"/>
+      <c r="H378" s="61"/>
+      <c r="I378" s="61"/>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="B379" s="36"/>
+      <c r="C379" s="36"/>
+      <c r="D379" s="36"/>
+      <c r="E379" s="36"/>
+      <c r="F379" s="36"/>
+      <c r="G379" s="36"/>
+      <c r="H379" s="61"/>
+      <c r="I379" s="61"/>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380" s="9" t="s">
+        <v>941</v>
+      </c>
+      <c r="B380" s="36"/>
+      <c r="C380" s="36"/>
+      <c r="D380" s="36"/>
+      <c r="E380" s="36"/>
+      <c r="F380" s="36"/>
+      <c r="G380" s="36"/>
+      <c r="H380" s="61"/>
+      <c r="I380" s="61"/>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="B381" s="36"/>
+      <c r="C381" s="36"/>
+      <c r="D381" s="36"/>
+      <c r="E381" s="36"/>
+      <c r="F381" s="36"/>
+      <c r="G381" s="36"/>
+      <c r="H381" s="61"/>
+      <c r="I381" s="61"/>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="B382" s="36"/>
+      <c r="C382" s="36"/>
+      <c r="D382" s="36"/>
+      <c r="E382" s="36"/>
+      <c r="F382" s="36"/>
+      <c r="G382" s="36"/>
+      <c r="H382" s="61"/>
+      <c r="I382" s="61"/>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B383" s="36"/>
+      <c r="C383" s="36"/>
+      <c r="D383" s="36"/>
+      <c r="E383" s="36"/>
+      <c r="F383" s="36"/>
+      <c r="G383" s="36"/>
+      <c r="H383" s="61"/>
+      <c r="I383" s="61"/>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="B384" s="36"/>
+      <c r="C384" s="36"/>
+      <c r="D384" s="36"/>
+      <c r="E384" s="36"/>
+      <c r="F384" s="36"/>
+      <c r="G384" s="36"/>
+      <c r="H384" s="61"/>
+      <c r="I384" s="61"/>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385" s="9" t="s">
+        <v>946</v>
+      </c>
+      <c r="B385" s="36"/>
+      <c r="C385" s="36"/>
+      <c r="D385" s="36"/>
+      <c r="E385" s="36"/>
+      <c r="F385" s="36"/>
+      <c r="G385" s="36"/>
+      <c r="H385" s="61"/>
+      <c r="I385" s="61"/>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="B386" s="36"/>
+      <c r="C386" s="36"/>
+      <c r="D386" s="36"/>
+      <c r="E386" s="36"/>
+      <c r="F386" s="36"/>
+      <c r="G386" s="36"/>
+      <c r="H386" s="61"/>
+      <c r="I386" s="61"/>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387" s="9" t="s">
+        <v>948</v>
+      </c>
+      <c r="B387" s="36"/>
+      <c r="C387" s="36"/>
+      <c r="D387" s="36"/>
+      <c r="E387" s="36"/>
+      <c r="F387" s="36"/>
+      <c r="G387" s="36"/>
+      <c r="H387" s="61"/>
+      <c r="I387" s="61"/>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="B388" s="36"/>
+      <c r="C388" s="36"/>
+      <c r="D388" s="36"/>
+      <c r="E388" s="36"/>
+      <c r="F388" s="36"/>
+      <c r="G388" s="36"/>
+      <c r="H388" s="61"/>
+      <c r="I388" s="61"/>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389" s="9" t="s">
+        <v>950</v>
+      </c>
+      <c r="B389" s="36"/>
+      <c r="C389" s="36"/>
+      <c r="D389" s="36"/>
+      <c r="E389" s="36"/>
+      <c r="F389" s="36"/>
+      <c r="G389" s="36"/>
+      <c r="H389" s="61"/>
+      <c r="I389" s="61"/>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390" s="9" t="s">
+        <v>951</v>
+      </c>
+      <c r="B390" s="36"/>
+      <c r="C390" s="36"/>
+      <c r="D390" s="36"/>
+      <c r="E390" s="36"/>
+      <c r="F390" s="36"/>
+      <c r="G390" s="36"/>
+      <c r="H390" s="61"/>
+      <c r="I390" s="61"/>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="B391" s="36"/>
+      <c r="C391" s="36"/>
+      <c r="D391" s="36"/>
+      <c r="E391" s="36"/>
+      <c r="F391" s="36"/>
+      <c r="G391" s="36"/>
+      <c r="H391" s="61"/>
+      <c r="I391" s="61"/>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="B392" s="36"/>
+      <c r="C392" s="36"/>
+      <c r="D392" s="36"/>
+      <c r="E392" s="36"/>
+      <c r="F392" s="36"/>
+      <c r="G392" s="36"/>
+      <c r="H392" s="61"/>
+      <c r="I392" s="61"/>
+    </row>
+    <row r="393" spans="1:9">
+      <c r="A393" s="9" t="s">
+        <v>954</v>
+      </c>
+      <c r="B393" s="36"/>
+      <c r="C393" s="36"/>
+      <c r="D393" s="36"/>
+      <c r="E393" s="36"/>
+      <c r="F393" s="36"/>
+      <c r="G393" s="36"/>
+      <c r="H393" s="61"/>
+      <c r="I393" s="61"/>
+    </row>
+    <row r="394" spans="1:9">
+      <c r="A394" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="B394" s="36"/>
+      <c r="C394" s="36"/>
+      <c r="D394" s="36"/>
+      <c r="E394" s="36"/>
+      <c r="F394" s="36"/>
+      <c r="G394" s="36"/>
+      <c r="H394" s="61"/>
+      <c r="I394" s="61"/>
+    </row>
+    <row r="395" spans="1:9">
+      <c r="A395" s="9" t="s">
+        <v>956</v>
+      </c>
+      <c r="B395" s="36"/>
+      <c r="C395" s="36"/>
+      <c r="D395" s="36"/>
+      <c r="E395" s="36"/>
+      <c r="F395" s="36"/>
+      <c r="G395" s="36"/>
+      <c r="H395" s="61"/>
+      <c r="I395" s="61"/>
+    </row>
+    <row r="396" spans="1:9">
+      <c r="A396" s="9" t="s">
+        <v>957</v>
+      </c>
+      <c r="B396" s="36"/>
+      <c r="C396" s="36"/>
+      <c r="D396" s="36"/>
+      <c r="E396" s="36"/>
+      <c r="F396" s="36"/>
+      <c r="G396" s="36"/>
+      <c r="H396" s="61"/>
+      <c r="I396" s="61"/>
+    </row>
+    <row r="397" spans="1:9">
+      <c r="A397" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="B397" s="36"/>
+      <c r="C397" s="36"/>
+      <c r="D397" s="36"/>
+      <c r="E397" s="36"/>
+      <c r="F397" s="36"/>
+      <c r="G397" s="36"/>
+      <c r="H397" s="61"/>
+      <c r="I397" s="61"/>
+    </row>
+    <row r="398" spans="1:9">
+      <c r="A398" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="B398" s="36"/>
+      <c r="C398" s="36"/>
+      <c r="D398" s="36"/>
+      <c r="E398" s="36"/>
+      <c r="F398" s="36"/>
+      <c r="G398" s="36"/>
+      <c r="H398" s="61"/>
+      <c r="I398" s="61"/>
+    </row>
+    <row r="399" spans="1:9">
+      <c r="A399" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="B399" s="36"/>
+      <c r="C399" s="36"/>
+      <c r="D399" s="36"/>
+      <c r="E399" s="36"/>
+      <c r="F399" s="36"/>
+      <c r="G399" s="36"/>
+      <c r="H399" s="61"/>
+      <c r="I399" s="61"/>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="B400" s="36"/>
+      <c r="C400" s="36"/>
+      <c r="D400" s="36"/>
+      <c r="E400" s="36"/>
+      <c r="F400" s="36"/>
+      <c r="G400" s="36"/>
+      <c r="H400" s="61"/>
+      <c r="I400" s="61"/>
+    </row>
+    <row r="401" spans="1:9">
+      <c r="A401" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="B401" s="36"/>
+      <c r="C401" s="36"/>
+      <c r="D401" s="36"/>
+      <c r="E401" s="36"/>
+      <c r="F401" s="36"/>
+      <c r="G401" s="36"/>
+      <c r="H401" s="61"/>
+      <c r="I401" s="61"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>